--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -276,7 +276,7 @@
         <v>39</v>
       </c>
       <c r="F4" t="n">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="G4" t="n">
         <v>0.0</v>
@@ -1472,7 +1472,7 @@
         <v>39</v>
       </c>
       <c r="F50" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="G50" t="n">
         <v>7.0</v>
@@ -3457,7 +3457,7 @@
         <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="F9" t="n">
         <v>15.0</v>
@@ -3483,7 +3483,7 @@
         <v>178.0</v>
       </c>
       <c r="F10" t="n">
-        <v>100.0</v>
+        <v>103.0</v>
       </c>
       <c r="G10" t="n">
         <v>272.0</v>
@@ -3552,7 +3552,7 @@
         <v>21.0</v>
       </c>
       <c r="F13" t="n">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -4019,7 +4019,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>131.0</v>
+        <v>135.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -4042,7 +4042,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>337.0</v>
+        <v>343.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -4065,7 +4065,7 @@
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>145.0</v>
+        <v>147.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -4088,7 +4088,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>263.0</v>
+        <v>271.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -4111,7 +4111,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>639.0</v>
+        <v>648.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -4318,7 +4318,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>407.0</v>
+        <v>411.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4364,7 +4364,7 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>417.0</v>
+        <v>430.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -4387,7 +4387,7 @@
         <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>3460.0</v>
+        <v>3483.0</v>
       </c>
       <c r="F18" t="n">
         <v>2.0</v>
@@ -4410,7 +4410,7 @@
         <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>1542.0</v>
+        <v>1546.0</v>
       </c>
       <c r="F19" t="n">
         <v>0.0</v>
@@ -4456,7 +4456,7 @@
         <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>601.0</v>
+        <v>607.0</v>
       </c>
       <c r="F21" t="n">
         <v>2.0</v>
@@ -4732,7 +4732,7 @@
         <v>17</v>
       </c>
       <c r="E33" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="F33" t="n">
         <v>0.0</v>
@@ -4755,7 +4755,7 @@
         <v>18</v>
       </c>
       <c r="E34" t="n">
-        <v>52.0</v>
+        <v>56.0</v>
       </c>
       <c r="F34" t="n">
         <v>0.0</v>
@@ -4985,7 +4985,7 @@
         <v>30</v>
       </c>
       <c r="E44" t="n">
-        <v>1089.0</v>
+        <v>1092.0</v>
       </c>
       <c r="F44" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -614,13 +614,13 @@
         <v>37</v>
       </c>
       <c r="F17" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="18">
@@ -1706,7 +1706,7 @@
         <v>37</v>
       </c>
       <c r="F59" t="n">
-        <v>1384.0</v>
+        <v>1385.0</v>
       </c>
       <c r="G59" t="n">
         <v>700.0</v>
@@ -1810,7 +1810,7 @@
         <v>38</v>
       </c>
       <c r="F63" t="n">
-        <v>154.0</v>
+        <v>156.0</v>
       </c>
       <c r="G63" t="n">
         <v>31.0</v>
@@ -1862,13 +1862,13 @@
         <v>37</v>
       </c>
       <c r="F65" t="n">
-        <v>215.0</v>
+        <v>221.0</v>
       </c>
       <c r="G65" t="n">
         <v>102.0</v>
       </c>
       <c r="H65" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="66">
@@ -2174,7 +2174,7 @@
         <v>37</v>
       </c>
       <c r="F77" t="n">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="G77" t="n">
         <v>1.0</v>
@@ -2619,7 +2619,7 @@
         <v>2.0</v>
       </c>
       <c r="G94" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="H94" t="n">
         <v>0.0</v>
@@ -3618,10 +3618,10 @@
         <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>127.0</v>
+        <v>135.0</v>
       </c>
       <c r="F16" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G16" t="n">
         <v>99.0</v>
@@ -3808,7 +3808,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="25">
@@ -4226,7 +4226,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>464.0</v>
+        <v>468.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4479,7 +4479,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9057.0</v>
+        <v>9058.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4502,7 +4502,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3099.0</v>
+        <v>3104.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -354,7 +354,7 @@
         <v>39</v>
       </c>
       <c r="F7" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
@@ -1784,7 +1784,7 @@
         <v>37</v>
       </c>
       <c r="F62" t="n">
-        <v>84.0</v>
+        <v>86.0</v>
       </c>
       <c r="G62" t="n">
         <v>9.0</v>
@@ -3480,7 +3480,7 @@
         <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>178.0</v>
+        <v>180.0</v>
       </c>
       <c r="F10" t="n">
         <v>103.0</v>
@@ -4042,7 +4042,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>343.0</v>
+        <v>344.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -4157,7 +4157,7 @@
         <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>659.0</v>
+        <v>662.0</v>
       </c>
       <c r="F8" t="n">
         <v>0.0</v>
@@ -4180,7 +4180,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1325.0</v>
+        <v>1329.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4272,7 +4272,7 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>100.0</v>
+        <v>104.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -4364,7 +4364,7 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>430.0</v>
+        <v>435.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -4410,7 +4410,7 @@
         <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>1546.0</v>
+        <v>1548.0</v>
       </c>
       <c r="F19" t="n">
         <v>0.0</v>
@@ -4502,7 +4502,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3104.0</v>
+        <v>3105.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4548,7 +4548,7 @@
         <v>23</v>
       </c>
       <c r="E25" t="n">
-        <v>3378.0</v>
+        <v>3387.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -4640,7 +4640,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1242.0</v>
+        <v>1244.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1264,7 +1264,7 @@
         <v>37</v>
       </c>
       <c r="F42" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G42" t="n">
         <v>0.0</v>
@@ -1810,7 +1810,7 @@
         <v>38</v>
       </c>
       <c r="F63" t="n">
-        <v>156.0</v>
+        <v>157.0</v>
       </c>
       <c r="G63" t="n">
         <v>31.0</v>
@@ -1836,7 +1836,7 @@
         <v>39</v>
       </c>
       <c r="F64" t="n">
-        <v>173.0</v>
+        <v>174.0</v>
       </c>
       <c r="G64" t="n">
         <v>1.0</v>
@@ -1862,7 +1862,7 @@
         <v>37</v>
       </c>
       <c r="F65" t="n">
-        <v>221.0</v>
+        <v>223.0</v>
       </c>
       <c r="G65" t="n">
         <v>102.0</v>
@@ -3785,7 +3785,7 @@
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="24">
@@ -3923,7 +3923,7 @@
         <v>0.0</v>
       </c>
       <c r="G29" t="n">
-        <v>105.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="30">
@@ -3963,7 +3963,7 @@
         <v>30</v>
       </c>
       <c r="E31" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4318,7 +4318,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>411.0</v>
+        <v>413.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4502,7 +4502,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3105.0</v>
+        <v>3113.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4525,7 +4525,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6112.0</v>
+        <v>6113.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4945,7 +4945,7 @@
         <v>0.0</v>
       </c>
       <c r="G42" t="n">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="43">
@@ -4962,7 +4962,7 @@
         <v>36</v>
       </c>
       <c r="E43" t="n">
-        <v>1243.0</v>
+        <v>1247.0</v>
       </c>
       <c r="F43" t="n">
         <v>0.0</v>
@@ -4985,7 +4985,7 @@
         <v>30</v>
       </c>
       <c r="E44" t="n">
-        <v>1092.0</v>
+        <v>1098.0</v>
       </c>
       <c r="F44" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -900,7 +900,7 @@
         <v>39</v>
       </c>
       <c r="F28" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G28" t="n">
         <v>0.0</v>
@@ -1862,7 +1862,7 @@
         <v>37</v>
       </c>
       <c r="F65" t="n">
-        <v>223.0</v>
+        <v>225.0</v>
       </c>
       <c r="G65" t="n">
         <v>102.0</v>
@@ -2200,7 +2200,7 @@
         <v>38</v>
       </c>
       <c r="F78" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="G78" t="n">
         <v>1.0</v>
@@ -2304,7 +2304,7 @@
         <v>39</v>
       </c>
       <c r="F82" t="n">
-        <v>93.0</v>
+        <v>94.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -3664,7 +3664,7 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="F18" t="n">
         <v>4.0</v>
@@ -3687,7 +3687,7 @@
         <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>104.0</v>
+        <v>108.0</v>
       </c>
       <c r="F19" t="n">
         <v>32.0</v>
@@ -4226,7 +4226,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>468.0</v>
+        <v>470.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4272,7 +4272,7 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>104.0</v>
+        <v>106.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -4318,7 +4318,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>413.0</v>
+        <v>420.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4502,7 +4502,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3113.0</v>
+        <v>3120.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4571,7 +4571,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>5683.0</v>
+        <v>5685.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4594,7 +4594,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>1588.0</v>
+        <v>1591.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -4640,7 +4640,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1244.0</v>
+        <v>1246.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4847,7 +4847,7 @@
         <v>24</v>
       </c>
       <c r="E38" t="n">
-        <v>2238.0</v>
+        <v>2239.0</v>
       </c>
       <c r="F38" t="n">
         <v>2.0</v>
@@ -4870,7 +4870,7 @@
         <v>25</v>
       </c>
       <c r="E39" t="n">
-        <v>1696.0</v>
+        <v>1698.0</v>
       </c>
       <c r="F39" t="n">
         <v>1.0</v>
@@ -4985,7 +4985,7 @@
         <v>30</v>
       </c>
       <c r="E44" t="n">
-        <v>1098.0</v>
+        <v>1110.0</v>
       </c>
       <c r="F44" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -666,7 +666,7 @@
         <v>39</v>
       </c>
       <c r="F19" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G19" t="n">
         <v>0.0</v>
@@ -1706,7 +1706,7 @@
         <v>37</v>
       </c>
       <c r="F59" t="n">
-        <v>1385.0</v>
+        <v>1388.0</v>
       </c>
       <c r="G59" t="n">
         <v>700.0</v>
@@ -1732,7 +1732,7 @@
         <v>38</v>
       </c>
       <c r="F60" t="n">
-        <v>259.0</v>
+        <v>261.0</v>
       </c>
       <c r="G60" t="n">
         <v>70.0</v>
@@ -1758,7 +1758,7 @@
         <v>39</v>
       </c>
       <c r="F61" t="n">
-        <v>267.0</v>
+        <v>268.0</v>
       </c>
       <c r="G61" t="n">
         <v>16.0</v>
@@ -1862,7 +1862,7 @@
         <v>37</v>
       </c>
       <c r="F65" t="n">
-        <v>225.0</v>
+        <v>236.0</v>
       </c>
       <c r="G65" t="n">
         <v>102.0</v>
@@ -1888,7 +1888,7 @@
         <v>38</v>
       </c>
       <c r="F66" t="n">
-        <v>205.0</v>
+        <v>207.0</v>
       </c>
       <c r="G66" t="n">
         <v>53.0</v>
@@ -1914,7 +1914,7 @@
         <v>39</v>
       </c>
       <c r="F67" t="n">
-        <v>121.0</v>
+        <v>122.0</v>
       </c>
       <c r="G67" t="n">
         <v>2.0</v>
@@ -2278,7 +2278,7 @@
         <v>38</v>
       </c>
       <c r="F81" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
       <c r="G81" t="n">
         <v>135.0</v>
@@ -4479,7 +4479,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9058.0</v>
+        <v>9076.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4502,7 +4502,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3120.0</v>
+        <v>3124.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4525,7 +4525,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6113.0</v>
+        <v>6117.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4640,7 +4640,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1246.0</v>
+        <v>1248.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -3756,7 +3756,7 @@
         <v>36</v>
       </c>
       <c r="E22" t="n">
-        <v>124.0</v>
+        <v>125.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
@@ -4985,7 +4985,7 @@
         <v>30</v>
       </c>
       <c r="E44" t="n">
-        <v>1110.0</v>
+        <v>1111.0</v>
       </c>
       <c r="F44" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1810,7 +1810,7 @@
         <v>38</v>
       </c>
       <c r="F63" t="n">
-        <v>157.0</v>
+        <v>158.0</v>
       </c>
       <c r="G63" t="n">
         <v>31.0</v>
@@ -1836,7 +1836,7 @@
         <v>39</v>
       </c>
       <c r="F64" t="n">
-        <v>174.0</v>
+        <v>175.0</v>
       </c>
       <c r="G64" t="n">
         <v>1.0</v>
@@ -2070,7 +2070,7 @@
         <v>39</v>
       </c>
       <c r="F73" t="n">
-        <v>245.0</v>
+        <v>247.0</v>
       </c>
       <c r="G73" t="n">
         <v>16.0</v>
@@ -3618,10 +3618,10 @@
         <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>135.0</v>
+        <v>139.0</v>
       </c>
       <c r="F16" t="n">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
       <c r="G16" t="n">
         <v>99.0</v>
@@ -3687,7 +3687,7 @@
         <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>108.0</v>
+        <v>111.0</v>
       </c>
       <c r="F19" t="n">
         <v>32.0</v>
@@ -4180,7 +4180,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1329.0</v>
+        <v>1331.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4502,7 +4502,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3124.0</v>
+        <v>3126.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4571,7 +4571,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>5685.0</v>
+        <v>5691.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1579,7 +1579,7 @@
         <v>0.0</v>
       </c>
       <c r="G54" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="H54" t="n">
         <v>0.0</v>
@@ -1836,7 +1836,7 @@
         <v>39</v>
       </c>
       <c r="F64" t="n">
-        <v>175.0</v>
+        <v>176.0</v>
       </c>
       <c r="G64" t="n">
         <v>1.0</v>
@@ -1966,7 +1966,7 @@
         <v>38</v>
       </c>
       <c r="F69" t="n">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
       <c r="G69" t="n">
         <v>21.0</v>
@@ -3480,7 +3480,7 @@
         <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>180.0</v>
+        <v>183.0</v>
       </c>
       <c r="F10" t="n">
         <v>103.0</v>
@@ -3503,7 +3503,7 @@
         <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="F11" t="n">
         <v>49.0</v>
@@ -3549,7 +3549,7 @@
         <v>21</v>
       </c>
       <c r="E13" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="F13" t="n">
         <v>20.0</v>
@@ -4088,7 +4088,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>271.0</v>
+        <v>272.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -4157,7 +4157,7 @@
         <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>662.0</v>
+        <v>666.0</v>
       </c>
       <c r="F8" t="n">
         <v>0.0</v>
@@ -4226,7 +4226,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>470.0</v>
+        <v>477.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4387,7 +4387,7 @@
         <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>3483.0</v>
+        <v>3491.0</v>
       </c>
       <c r="F18" t="n">
         <v>2.0</v>
@@ -4456,7 +4456,7 @@
         <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>607.0</v>
+        <v>617.0</v>
       </c>
       <c r="F21" t="n">
         <v>2.0</v>
@@ -4502,7 +4502,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3126.0</v>
+        <v>3127.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4548,7 +4548,7 @@
         <v>23</v>
       </c>
       <c r="E25" t="n">
-        <v>3387.0</v>
+        <v>3388.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1056,7 +1056,7 @@
         <v>38</v>
       </c>
       <c r="F34" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -2070,7 +2070,7 @@
         <v>39</v>
       </c>
       <c r="F73" t="n">
-        <v>247.0</v>
+        <v>248.0</v>
       </c>
       <c r="G73" t="n">
         <v>16.0</v>
@@ -2252,7 +2252,7 @@
         <v>37</v>
       </c>
       <c r="F80" t="n">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="G80" t="n">
         <v>138.0</v>
@@ -2408,7 +2408,7 @@
         <v>38</v>
       </c>
       <c r="F86" t="n">
-        <v>82.0</v>
+        <v>83.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -3214,7 +3214,7 @@
         <v>38</v>
       </c>
       <c r="F117" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="G117" t="n">
         <v>9.0</v>
@@ -3687,7 +3687,7 @@
         <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>111.0</v>
+        <v>114.0</v>
       </c>
       <c r="F19" t="n">
         <v>32.0</v>
@@ -3710,7 +3710,7 @@
         <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>191.0</v>
+        <v>193.0</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
@@ -3940,7 +3940,7 @@
         <v>36</v>
       </c>
       <c r="E30" t="n">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="F30" t="n">
         <v>0.0</v>
@@ -3963,7 +3963,7 @@
         <v>30</v>
       </c>
       <c r="E31" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4226,7 +4226,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>477.0</v>
+        <v>480.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4318,7 +4318,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>420.0</v>
+        <v>429.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4416,7 +4416,7 @@
         <v>0.0</v>
       </c>
       <c r="G19" t="n">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
     </row>
     <row r="20">
@@ -4502,7 +4502,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3127.0</v>
+        <v>3145.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4571,7 +4571,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>5691.0</v>
+        <v>5696.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4617,7 +4617,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>4410.0</v>
+        <v>4411.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>
@@ -4640,7 +4640,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1248.0</v>
+        <v>1249.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4686,7 +4686,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>1862.0</v>
+        <v>1864.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4962,7 +4962,7 @@
         <v>36</v>
       </c>
       <c r="E43" t="n">
-        <v>1247.0</v>
+        <v>1251.0</v>
       </c>
       <c r="F43" t="n">
         <v>0.0</v>
@@ -4985,7 +4985,7 @@
         <v>30</v>
       </c>
       <c r="E44" t="n">
-        <v>1111.0</v>
+        <v>1115.0</v>
       </c>
       <c r="F44" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -588,7 +588,7 @@
         <v>39</v>
       </c>
       <c r="F16" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -614,7 +614,7 @@
         <v>37</v>
       </c>
       <c r="F17" t="n">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -874,7 +874,7 @@
         <v>38</v>
       </c>
       <c r="F27" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
@@ -1056,7 +1056,7 @@
         <v>38</v>
       </c>
       <c r="F34" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1706,7 +1706,7 @@
         <v>37</v>
       </c>
       <c r="F59" t="n">
-        <v>1388.0</v>
+        <v>1390.0</v>
       </c>
       <c r="G59" t="n">
         <v>700.0</v>
@@ -1758,7 +1758,7 @@
         <v>39</v>
       </c>
       <c r="F61" t="n">
-        <v>268.0</v>
+        <v>269.0</v>
       </c>
       <c r="G61" t="n">
         <v>16.0</v>
@@ -1810,7 +1810,7 @@
         <v>38</v>
       </c>
       <c r="F63" t="n">
-        <v>158.0</v>
+        <v>159.0</v>
       </c>
       <c r="G63" t="n">
         <v>31.0</v>
@@ -1836,7 +1836,7 @@
         <v>39</v>
       </c>
       <c r="F64" t="n">
-        <v>176.0</v>
+        <v>178.0</v>
       </c>
       <c r="G64" t="n">
         <v>1.0</v>
@@ -1862,7 +1862,7 @@
         <v>37</v>
       </c>
       <c r="F65" t="n">
-        <v>236.0</v>
+        <v>240.0</v>
       </c>
       <c r="G65" t="n">
         <v>102.0</v>
@@ -2203,7 +2203,7 @@
         <v>58.0</v>
       </c>
       <c r="G78" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H78" t="n">
         <v>3.0</v>
@@ -3480,7 +3480,7 @@
         <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>183.0</v>
+        <v>185.0</v>
       </c>
       <c r="F10" t="n">
         <v>103.0</v>
@@ -3503,7 +3503,7 @@
         <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="F11" t="n">
         <v>49.0</v>
@@ -3693,7 +3693,7 @@
         <v>32.0</v>
       </c>
       <c r="G19" t="n">
-        <v>13.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="20">
@@ -4111,7 +4111,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>648.0</v>
+        <v>650.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -4180,7 +4180,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1331.0</v>
+        <v>1337.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4226,7 +4226,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>480.0</v>
+        <v>486.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4318,7 +4318,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>429.0</v>
+        <v>431.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4479,7 +4479,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9076.0</v>
+        <v>9086.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4502,7 +4502,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3145.0</v>
+        <v>3148.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4525,7 +4525,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6117.0</v>
+        <v>6126.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4571,7 +4571,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>5696.0</v>
+        <v>5697.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4640,7 +4640,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1249.0</v>
+        <v>1250.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4985,7 +4985,7 @@
         <v>30</v>
       </c>
       <c r="E44" t="n">
-        <v>1115.0</v>
+        <v>1124.0</v>
       </c>
       <c r="F44" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -2018,7 +2018,7 @@
         <v>37</v>
       </c>
       <c r="F71" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="G71" t="n">
         <v>244.0</v>
@@ -3690,7 +3690,7 @@
         <v>114.0</v>
       </c>
       <c r="F19" t="n">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
       <c r="G19" t="n">
         <v>15.0</v>
@@ -3710,7 +3710,7 @@
         <v>28</v>
       </c>
       <c r="E20" t="n">
-        <v>193.0</v>
+        <v>195.0</v>
       </c>
       <c r="F20" t="n">
         <v>0.0</v>
@@ -4180,7 +4180,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1337.0</v>
+        <v>1343.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4203,7 +4203,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1768.0</v>
+        <v>1778.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -4226,7 +4226,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>486.0</v>
+        <v>490.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4272,7 +4272,7 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>106.0</v>
+        <v>108.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -4502,7 +4502,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3148.0</v>
+        <v>3149.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4525,7 +4525,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6126.0</v>
+        <v>6128.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4571,7 +4571,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>5697.0</v>
+        <v>5704.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4893,7 +4893,7 @@
         <v>26</v>
       </c>
       <c r="E40" t="n">
-        <v>598.0</v>
+        <v>599.0</v>
       </c>
       <c r="F40" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -3214,7 +3214,7 @@
         <v>38</v>
       </c>
       <c r="F117" t="n">
-        <v>30.0</v>
+        <v>32.0</v>
       </c>
       <c r="G117" t="n">
         <v>9.0</v>
@@ -4985,7 +4985,7 @@
         <v>30</v>
       </c>
       <c r="E44" t="n">
-        <v>1124.0</v>
+        <v>1127.0</v>
       </c>
       <c r="F44" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -614,7 +614,7 @@
         <v>37</v>
       </c>
       <c r="F17" t="n">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
@@ -1862,7 +1862,7 @@
         <v>37</v>
       </c>
       <c r="F65" t="n">
-        <v>240.0</v>
+        <v>243.0</v>
       </c>
       <c r="G65" t="n">
         <v>102.0</v>
@@ -3480,7 +3480,7 @@
         <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>185.0</v>
+        <v>186.0</v>
       </c>
       <c r="F10" t="n">
         <v>103.0</v>
@@ -3618,7 +3618,7 @@
         <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>139.0</v>
+        <v>143.0</v>
       </c>
       <c r="F16" t="n">
         <v>28.0</v>
@@ -3687,7 +3687,7 @@
         <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>114.0</v>
+        <v>116.0</v>
       </c>
       <c r="F19" t="n">
         <v>35.0</v>
@@ -4042,7 +4042,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>344.0</v>
+        <v>348.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -4065,7 +4065,7 @@
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>147.0</v>
+        <v>148.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -4111,7 +4111,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>650.0</v>
+        <v>658.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -4364,7 +4364,7 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>435.0</v>
+        <v>436.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -4387,7 +4387,7 @@
         <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>3491.0</v>
+        <v>3501.0</v>
       </c>
       <c r="F18" t="n">
         <v>2.0</v>
@@ -4456,7 +4456,7 @@
         <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>617.0</v>
+        <v>621.0</v>
       </c>
       <c r="F21" t="n">
         <v>2.0</v>
@@ -4502,7 +4502,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3149.0</v>
+        <v>3156.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4525,7 +4525,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6128.0</v>
+        <v>6130.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4571,7 +4571,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>5704.0</v>
+        <v>5706.0</v>
       </c>
       <c r="F26" t="n">
         <v>1.0</v>
@@ -4594,7 +4594,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>1591.0</v>
+        <v>1592.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -4617,7 +4617,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>4411.0</v>
+        <v>4412.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>
@@ -4755,7 +4755,7 @@
         <v>18</v>
       </c>
       <c r="E34" t="n">
-        <v>56.0</v>
+        <v>58.0</v>
       </c>
       <c r="F34" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -978,7 +978,7 @@
         <v>39</v>
       </c>
       <c r="F31" t="n">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -1706,7 +1706,7 @@
         <v>37</v>
       </c>
       <c r="F59" t="n">
-        <v>1390.0</v>
+        <v>1393.0</v>
       </c>
       <c r="G59" t="n">
         <v>700.0</v>
@@ -1816,7 +1816,7 @@
         <v>31.0</v>
       </c>
       <c r="H63" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="64">
@@ -2044,7 +2044,7 @@
         <v>38</v>
       </c>
       <c r="F72" t="n">
-        <v>168.0</v>
+        <v>170.0</v>
       </c>
       <c r="G72" t="n">
         <v>123.0</v>
@@ -2798,7 +2798,7 @@
         <v>39</v>
       </c>
       <c r="F101" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="G101" t="n">
         <v>3.0</v>
@@ -3664,7 +3664,7 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="F18" t="n">
         <v>4.0</v>
@@ -4157,7 +4157,7 @@
         <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>666.0</v>
+        <v>667.0</v>
       </c>
       <c r="F8" t="n">
         <v>0.0</v>
@@ -4180,7 +4180,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1343.0</v>
+        <v>1344.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4479,7 +4479,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9086.0</v>
+        <v>9092.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4548,7 +4548,7 @@
         <v>23</v>
       </c>
       <c r="E25" t="n">
-        <v>3388.0</v>
+        <v>3390.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -4617,7 +4617,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>4412.0</v>
+        <v>4414.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="40">
   <si>
     <t>Area</t>
   </si>
@@ -1004,7 +1004,7 @@
         <v>39</v>
       </c>
       <c r="F32" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1810,7 +1810,7 @@
         <v>38</v>
       </c>
       <c r="F63" t="n">
-        <v>159.0</v>
+        <v>160.0</v>
       </c>
       <c r="G63" t="n">
         <v>31.0</v>
@@ -1836,7 +1836,7 @@
         <v>39</v>
       </c>
       <c r="F64" t="n">
-        <v>178.0</v>
+        <v>180.0</v>
       </c>
       <c r="G64" t="n">
         <v>1.0</v>
@@ -1862,10 +1862,10 @@
         <v>37</v>
       </c>
       <c r="F65" t="n">
-        <v>243.0</v>
+        <v>244.0</v>
       </c>
       <c r="G65" t="n">
-        <v>102.0</v>
+        <v>114.0</v>
       </c>
       <c r="H65" t="n">
         <v>7.0</v>
@@ -1888,7 +1888,7 @@
         <v>38</v>
       </c>
       <c r="F66" t="n">
-        <v>207.0</v>
+        <v>208.0</v>
       </c>
       <c r="G66" t="n">
         <v>53.0</v>
@@ -2018,10 +2018,10 @@
         <v>37</v>
       </c>
       <c r="F71" t="n">
-        <v>133.0</v>
+        <v>157.0</v>
       </c>
       <c r="G71" t="n">
-        <v>244.0</v>
+        <v>305.0</v>
       </c>
       <c r="H71" t="n">
         <v>0.0</v>
@@ -2044,10 +2044,10 @@
         <v>38</v>
       </c>
       <c r="F72" t="n">
-        <v>170.0</v>
+        <v>201.0</v>
       </c>
       <c r="G72" t="n">
-        <v>123.0</v>
+        <v>141.0</v>
       </c>
       <c r="H72" t="n">
         <v>3.0</v>
@@ -2070,10 +2070,10 @@
         <v>39</v>
       </c>
       <c r="F73" t="n">
-        <v>248.0</v>
+        <v>295.0</v>
       </c>
       <c r="G73" t="n">
-        <v>16.0</v>
+        <v>19.0</v>
       </c>
       <c r="H73" t="n">
         <v>0.0</v>
@@ -2096,10 +2096,10 @@
         <v>37</v>
       </c>
       <c r="F74" t="n">
-        <v>76.0</v>
+        <v>80.0</v>
       </c>
       <c r="G74" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H74" t="n">
         <v>0.0</v>
@@ -2122,13 +2122,13 @@
         <v>38</v>
       </c>
       <c r="F75" t="n">
-        <v>50.0</v>
+        <v>71.0</v>
       </c>
       <c r="G75" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="76">
@@ -2148,7 +2148,7 @@
         <v>39</v>
       </c>
       <c r="F76" t="n">
-        <v>41.0</v>
+        <v>51.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -2174,7 +2174,7 @@
         <v>37</v>
       </c>
       <c r="F77" t="n">
-        <v>41.0</v>
+        <v>46.0</v>
       </c>
       <c r="G77" t="n">
         <v>1.0</v>
@@ -2200,13 +2200,13 @@
         <v>38</v>
       </c>
       <c r="F78" t="n">
-        <v>58.0</v>
+        <v>80.0</v>
       </c>
       <c r="G78" t="n">
         <v>2.0</v>
       </c>
       <c r="H78" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="79">
@@ -2226,7 +2226,7 @@
         <v>39</v>
       </c>
       <c r="F79" t="n">
-        <v>63.0</v>
+        <v>65.0</v>
       </c>
       <c r="G79" t="n">
         <v>0.0</v>
@@ -2408,7 +2408,7 @@
         <v>38</v>
       </c>
       <c r="F86" t="n">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -2711,10 +2711,10 @@
         <v>11</v>
       </c>
       <c r="C98" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D98" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E98" t="s">
         <v>37</v>
@@ -2723,7 +2723,7 @@
         <v>1.0</v>
       </c>
       <c r="G98" t="n">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="H98" t="n">
         <v>0.0</v>
@@ -2737,19 +2737,19 @@
         <v>11</v>
       </c>
       <c r="C99" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D99" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E99" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F99" t="n">
-        <v>24.0</v>
+        <v>2.0</v>
       </c>
       <c r="G99" t="n">
-        <v>61.0</v>
+        <v>0.0</v>
       </c>
       <c r="H99" t="n">
         <v>0.0</v>
@@ -2763,19 +2763,19 @@
         <v>11</v>
       </c>
       <c r="C100" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D100" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E100" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F100" t="n">
-        <v>31.0</v>
+        <v>4.0</v>
       </c>
       <c r="G100" t="n">
-        <v>18.0</v>
+        <v>0.0</v>
       </c>
       <c r="H100" t="n">
         <v>0.0</v>
@@ -2789,19 +2789,19 @@
         <v>11</v>
       </c>
       <c r="C101" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D101" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E101" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F101" t="n">
-        <v>47.0</v>
+        <v>0.0</v>
       </c>
       <c r="G101" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2815,19 +2815,19 @@
         <v>11</v>
       </c>
       <c r="C102" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D102" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E102" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F102" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="G102" t="n">
-        <v>1.0</v>
+        <v>19.0</v>
       </c>
       <c r="H102" t="n">
         <v>0.0</v>
@@ -2841,22 +2841,22 @@
         <v>11</v>
       </c>
       <c r="C103" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D103" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E103" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F103" t="n">
-        <v>21.0</v>
+        <v>16.0</v>
       </c>
       <c r="G103" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="H103" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="104">
@@ -2867,22 +2867,22 @@
         <v>11</v>
       </c>
       <c r="C104" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D104" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E104" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F104" t="n">
-        <v>10.0</v>
+        <v>59.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
       </c>
       <c r="H104" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="105">
@@ -2893,16 +2893,16 @@
         <v>11</v>
       </c>
       <c r="C105" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D105" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="E105" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F105" t="n">
-        <v>5.0</v>
+        <v>15.0</v>
       </c>
       <c r="G105" t="n">
         <v>0.0</v>
@@ -2919,22 +2919,22 @@
         <v>11</v>
       </c>
       <c r="C106" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D106" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E106" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F106" t="n">
-        <v>22.0</v>
+        <v>6.0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="H106" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="107">
@@ -2945,19 +2945,19 @@
         <v>11</v>
       </c>
       <c r="C107" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D107" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E107" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F107" t="n">
-        <v>2.0</v>
+        <v>32.0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.0</v>
+        <v>9.0</v>
       </c>
       <c r="H107" t="n">
         <v>0.0</v>
@@ -2974,278 +2974,18 @@
         <v>16</v>
       </c>
       <c r="D108" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E108" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F108" t="n">
-        <v>1.0</v>
+        <v>35.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
       </c>
       <c r="H108" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>8</v>
-      </c>
-      <c r="B109" t="s">
-        <v>11</v>
-      </c>
-      <c r="C109" t="s">
-        <v>16</v>
-      </c>
-      <c r="D109" t="s">
-        <v>28</v>
-      </c>
-      <c r="E109" t="s">
-        <v>38</v>
-      </c>
-      <c r="F109" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G109" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>8</v>
-      </c>
-      <c r="B110" t="s">
-        <v>11</v>
-      </c>
-      <c r="C110" t="s">
-        <v>16</v>
-      </c>
-      <c r="D110" t="s">
-        <v>28</v>
-      </c>
-      <c r="E110" t="s">
-        <v>39</v>
-      </c>
-      <c r="F110" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="G110" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H110" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>8</v>
-      </c>
-      <c r="B111" t="s">
-        <v>11</v>
-      </c>
-      <c r="C111" t="s">
-        <v>16</v>
-      </c>
-      <c r="D111" t="s">
-        <v>35</v>
-      </c>
-      <c r="E111" t="s">
-        <v>37</v>
-      </c>
-      <c r="F111" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G111" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="H111" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>8</v>
-      </c>
-      <c r="B112" t="s">
-        <v>11</v>
-      </c>
-      <c r="C112" t="s">
-        <v>16</v>
-      </c>
-      <c r="D112" t="s">
-        <v>35</v>
-      </c>
-      <c r="E112" t="s">
-        <v>38</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G112" t="n">
-        <v>19.0</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>8</v>
-      </c>
-      <c r="B113" t="s">
-        <v>11</v>
-      </c>
-      <c r="C113" t="s">
-        <v>16</v>
-      </c>
-      <c r="D113" t="s">
-        <v>36</v>
-      </c>
-      <c r="E113" t="s">
-        <v>37</v>
-      </c>
-      <c r="F113" t="n">
-        <v>16.0</v>
-      </c>
-      <c r="G113" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>8</v>
-      </c>
-      <c r="B114" t="s">
-        <v>11</v>
-      </c>
-      <c r="C114" t="s">
-        <v>16</v>
-      </c>
-      <c r="D114" t="s">
-        <v>36</v>
-      </c>
-      <c r="E114" t="s">
-        <v>38</v>
-      </c>
-      <c r="F114" t="n">
-        <v>58.0</v>
-      </c>
-      <c r="G114" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H114" t="n">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>8</v>
-      </c>
-      <c r="B115" t="s">
-        <v>11</v>
-      </c>
-      <c r="C115" t="s">
-        <v>16</v>
-      </c>
-      <c r="D115" t="s">
-        <v>36</v>
-      </c>
-      <c r="E115" t="s">
-        <v>39</v>
-      </c>
-      <c r="F115" t="n">
-        <v>15.0</v>
-      </c>
-      <c r="G115" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>8</v>
-      </c>
-      <c r="B116" t="s">
-        <v>11</v>
-      </c>
-      <c r="C116" t="s">
-        <v>16</v>
-      </c>
-      <c r="D116" t="s">
-        <v>30</v>
-      </c>
-      <c r="E116" t="s">
-        <v>37</v>
-      </c>
-      <c r="F116" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="G116" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>8</v>
-      </c>
-      <c r="B117" t="s">
-        <v>11</v>
-      </c>
-      <c r="C117" t="s">
-        <v>16</v>
-      </c>
-      <c r="D117" t="s">
-        <v>30</v>
-      </c>
-      <c r="E117" t="s">
-        <v>38</v>
-      </c>
-      <c r="F117" t="n">
-        <v>32.0</v>
-      </c>
-      <c r="G117" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>8</v>
-      </c>
-      <c r="B118" t="s">
-        <v>11</v>
-      </c>
-      <c r="C118" t="s">
-        <v>16</v>
-      </c>
-      <c r="D118" t="s">
-        <v>30</v>
-      </c>
-      <c r="E118" t="s">
-        <v>39</v>
-      </c>
-      <c r="F118" t="n">
-        <v>35.0</v>
-      </c>
-      <c r="G118" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H118" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -3457,7 +3197,7 @@
         <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="F9" t="n">
         <v>15.0</v>
@@ -3618,7 +3358,7 @@
         <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>143.0</v>
+        <v>146.0</v>
       </c>
       <c r="F16" t="n">
         <v>28.0</v>
@@ -3664,13 +3404,13 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>39.0</v>
+        <v>56.0</v>
       </c>
       <c r="F18" t="n">
-        <v>4.0</v>
+        <v>15.0</v>
       </c>
       <c r="G18" t="n">
-        <v>25.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="19">
@@ -3684,16 +3424,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E19" t="n">
-        <v>116.0</v>
+        <v>4.0</v>
       </c>
       <c r="F19" t="n">
-        <v>35.0</v>
+        <v>5.0</v>
       </c>
       <c r="G19" t="n">
-        <v>15.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="20">
@@ -3704,19 +3444,19 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>195.0</v>
+        <v>116.0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0</v>
+        <v>37.0</v>
       </c>
       <c r="G20" t="n">
-        <v>139.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="21">
@@ -3730,16 +3470,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0</v>
+        <v>195.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>122.0</v>
+        <v>139.0</v>
       </c>
     </row>
     <row r="22">
@@ -3753,16 +3493,16 @@
         <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22" t="n">
-        <v>125.0</v>
+        <v>0.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0</v>
+        <v>122.0</v>
       </c>
     </row>
     <row r="23">
@@ -3770,22 +3510,22 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D23" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0</v>
+        <v>125.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
       </c>
       <c r="G23" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
@@ -3799,16 +3539,16 @@
         <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E24" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="25">
@@ -3819,19 +3559,19 @@
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="26">
@@ -3842,19 +3582,19 @@
         <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E26" t="n">
-        <v>17.0</v>
+        <v>0.0</v>
       </c>
       <c r="F26" t="n">
-        <v>11.0</v>
+        <v>0.0</v>
       </c>
       <c r="G26" t="n">
-        <v>12.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="27">
@@ -3865,19 +3605,19 @@
         <v>11</v>
       </c>
       <c r="C27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E27" t="n">
-        <v>4.0</v>
+        <v>77.0</v>
       </c>
       <c r="F27" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
@@ -3888,87 +3628,18 @@
         <v>11</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0</v>
+        <v>12.0</v>
       </c>
       <c r="F28" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" t="s">
-        <v>16</v>
-      </c>
-      <c r="D29" t="s">
-        <v>35</v>
-      </c>
-      <c r="E29" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>106.0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" t="s">
-        <v>16</v>
-      </c>
-      <c r="D30" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" t="n">
-        <v>77.0</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" t="s">
-        <v>16</v>
-      </c>
-      <c r="D31" t="s">
-        <v>30</v>
-      </c>
-      <c r="E31" t="n">
-        <v>12.0</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G31" t="n">
         <v>2.0</v>
       </c>
     </row>
@@ -4019,7 +3690,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>135.0</v>
+        <v>143.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -4180,7 +3851,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1344.0</v>
+        <v>1347.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4203,7 +3874,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1778.0</v>
+        <v>1781.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -4226,7 +3897,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>490.0</v>
+        <v>503.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4272,7 +3943,7 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>108.0</v>
+        <v>109.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -4318,7 +3989,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>431.0</v>
+        <v>432.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4502,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3156.0</v>
+        <v>3161.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4525,7 +4196,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6130.0</v>
+        <v>6145.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4571,13 +4242,13 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>5706.0</v>
+        <v>7966.0</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G26" t="n">
-        <v>164.0</v>
+        <v>213.0</v>
       </c>
     </row>
     <row r="27">
@@ -4594,13 +4265,13 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>1592.0</v>
+        <v>3299.0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G27" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
     </row>
     <row r="28">
@@ -4617,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>4414.0</v>
+        <v>5018.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>
@@ -4640,7 +4311,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1250.0</v>
+        <v>1256.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4686,7 +4357,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>1864.0</v>
+        <v>1872.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4818,13 +4489,13 @@
         <v>11</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E37" t="n">
-        <v>14.0</v>
+        <v>94.0</v>
       </c>
       <c r="F37" t="n">
         <v>0.0</v>
@@ -4841,19 +4512,19 @@
         <v>11</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E38" t="n">
-        <v>2239.0</v>
+        <v>0.0</v>
       </c>
       <c r="F38" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="G38" t="n">
-        <v>49.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="39">
@@ -4864,19 +4535,19 @@
         <v>11</v>
       </c>
       <c r="C39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D39" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E39" t="n">
-        <v>1698.0</v>
+        <v>1256.0</v>
       </c>
       <c r="F39" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G39" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="40">
@@ -4887,110 +4558,18 @@
         <v>11</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D40" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>599.0</v>
+        <v>1133.0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" t="s">
-        <v>16</v>
-      </c>
-      <c r="D41" t="s">
-        <v>28</v>
-      </c>
-      <c r="E41" t="n">
-        <v>94.0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42" t="s">
-        <v>16</v>
-      </c>
-      <c r="D42" t="s">
-        <v>35</v>
-      </c>
-      <c r="E42" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>15.0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>8</v>
-      </c>
-      <c r="B43" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" t="s">
-        <v>16</v>
-      </c>
-      <c r="D43" t="s">
-        <v>36</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1251.0</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44" t="s">
-        <v>11</v>
-      </c>
-      <c r="C44" t="s">
-        <v>16</v>
-      </c>
-      <c r="D44" t="s">
-        <v>30</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1127.0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G44" t="n">
         <v>10.0</v>
       </c>
     </row>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1212,7 +1212,7 @@
         <v>38</v>
       </c>
       <c r="F40" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -3611,7 +3611,7 @@
         <v>36</v>
       </c>
       <c r="E27" t="n">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -3634,7 +3634,7 @@
         <v>30</v>
       </c>
       <c r="E28" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -3897,7 +3897,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>503.0</v>
+        <v>506.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3989,7 +3989,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>432.0</v>
+        <v>434.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4150,7 +4150,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9092.0</v>
+        <v>9094.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4173,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3161.0</v>
+        <v>3163.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4202,7 +4202,7 @@
         <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="25">
@@ -4242,7 +4242,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>7966.0</v>
+        <v>7970.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4265,7 +4265,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>3299.0</v>
+        <v>3300.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4564,7 +4564,7 @@
         <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>1133.0</v>
+        <v>1142.0</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1862,10 +1862,10 @@
         <v>37</v>
       </c>
       <c r="F65" t="n">
-        <v>244.0</v>
+        <v>245.0</v>
       </c>
       <c r="G65" t="n">
-        <v>114.0</v>
+        <v>115.0</v>
       </c>
       <c r="H65" t="n">
         <v>7.0</v>
@@ -2278,7 +2278,7 @@
         <v>38</v>
       </c>
       <c r="F81" t="n">
-        <v>101.0</v>
+        <v>102.0</v>
       </c>
       <c r="G81" t="n">
         <v>135.0</v>
@@ -3450,7 +3450,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>116.0</v>
+        <v>119.0</v>
       </c>
       <c r="F20" t="n">
         <v>37.0</v>
@@ -3897,7 +3897,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>506.0</v>
+        <v>508.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4150,7 +4150,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9094.0</v>
+        <v>9097.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4173,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3163.0</v>
+        <v>3165.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4294,7 +4294,7 @@
         <v>1.0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="29">
@@ -4311,7 +4311,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1256.0</v>
+        <v>1261.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4357,7 +4357,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>1872.0</v>
+        <v>1874.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4564,7 +4564,7 @@
         <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>1142.0</v>
+        <v>1143.0</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1030,7 +1030,7 @@
         <v>37</v>
       </c>
       <c r="F33" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -2252,7 +2252,7 @@
         <v>37</v>
       </c>
       <c r="F80" t="n">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="G80" t="n">
         <v>138.0</v>
@@ -4311,7 +4311,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1261.0</v>
+        <v>1262.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4357,7 +4357,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>1874.0</v>
+        <v>1877.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -614,13 +614,13 @@
         <v>37</v>
       </c>
       <c r="F17" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="G17" t="n">
         <v>0.0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="18">
@@ -874,7 +874,7 @@
         <v>38</v>
       </c>
       <c r="F27" t="n">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
@@ -1706,10 +1706,10 @@
         <v>37</v>
       </c>
       <c r="F59" t="n">
-        <v>1393.0</v>
+        <v>1394.0</v>
       </c>
       <c r="G59" t="n">
-        <v>700.0</v>
+        <v>701.0</v>
       </c>
       <c r="H59" t="n">
         <v>92.0</v>
@@ -1862,7 +1862,7 @@
         <v>37</v>
       </c>
       <c r="F65" t="n">
-        <v>245.0</v>
+        <v>246.0</v>
       </c>
       <c r="G65" t="n">
         <v>115.0</v>
@@ -2148,7 +2148,7 @@
         <v>39</v>
       </c>
       <c r="F76" t="n">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -3358,10 +3358,10 @@
         <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>146.0</v>
+        <v>149.0</v>
       </c>
       <c r="F16" t="n">
-        <v>28.0</v>
+        <v>25.0</v>
       </c>
       <c r="G16" t="n">
         <v>99.0</v>
@@ -3851,7 +3851,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1347.0</v>
+        <v>1352.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3874,7 +3874,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1781.0</v>
+        <v>1782.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -3897,7 +3897,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>508.0</v>
+        <v>523.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4150,7 +4150,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9097.0</v>
+        <v>9107.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4196,7 +4196,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6145.0</v>
+        <v>6146.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4242,7 +4242,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>7970.0</v>
+        <v>7984.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4265,7 +4265,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>3300.0</v>
+        <v>3303.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4288,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5018.0</v>
+        <v>5021.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -978,7 +978,7 @@
         <v>39</v>
       </c>
       <c r="F31" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -1810,7 +1810,7 @@
         <v>38</v>
       </c>
       <c r="F63" t="n">
-        <v>160.0</v>
+        <v>162.0</v>
       </c>
       <c r="G63" t="n">
         <v>31.0</v>
@@ -1888,7 +1888,7 @@
         <v>38</v>
       </c>
       <c r="F66" t="n">
-        <v>208.0</v>
+        <v>209.0</v>
       </c>
       <c r="G66" t="n">
         <v>53.0</v>
@@ -1966,7 +1966,7 @@
         <v>38</v>
       </c>
       <c r="F69" t="n">
-        <v>83.0</v>
+        <v>84.0</v>
       </c>
       <c r="G69" t="n">
         <v>21.0</v>
@@ -3358,7 +3358,7 @@
         <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
       <c r="F16" t="n">
         <v>25.0</v>
@@ -3450,7 +3450,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>119.0</v>
+        <v>121.0</v>
       </c>
       <c r="F20" t="n">
         <v>37.0</v>
@@ -3828,7 +3828,7 @@
         <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>667.0</v>
+        <v>669.0</v>
       </c>
       <c r="F8" t="n">
         <v>0.0</v>
@@ -3874,7 +3874,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1782.0</v>
+        <v>1783.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -3897,7 +3897,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>523.0</v>
+        <v>529.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4173,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3165.0</v>
+        <v>3167.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4196,7 +4196,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6146.0</v>
+        <v>6163.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4219,7 +4219,7 @@
         <v>23</v>
       </c>
       <c r="E25" t="n">
-        <v>3390.0</v>
+        <v>3395.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -4288,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5021.0</v>
+        <v>5033.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -2304,7 +2304,7 @@
         <v>39</v>
       </c>
       <c r="F82" t="n">
-        <v>94.0</v>
+        <v>99.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -2931,7 +2931,7 @@
         <v>6.0</v>
       </c>
       <c r="G106" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="H106" t="n">
         <v>0.0</v>
@@ -3943,7 +3943,7 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>109.0</v>
+        <v>110.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3989,7 +3989,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>434.0</v>
+        <v>437.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4173,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3167.0</v>
+        <v>3184.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4311,7 +4311,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1262.0</v>
+        <v>1270.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4357,7 +4357,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>1877.0</v>
+        <v>1888.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4541,7 +4541,7 @@
         <v>36</v>
       </c>
       <c r="E39" t="n">
-        <v>1256.0</v>
+        <v>1275.0</v>
       </c>
       <c r="F39" t="n">
         <v>0.0</v>
@@ -4564,7 +4564,7 @@
         <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>1143.0</v>
+        <v>1146.0</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -646,7 +646,7 @@
         <v>0.0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="19">
@@ -1108,7 +1108,7 @@
         <v>37</v>
       </c>
       <c r="F36" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -1160,7 +1160,7 @@
         <v>39</v>
       </c>
       <c r="F38" t="n">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1810,7 +1810,7 @@
         <v>38</v>
       </c>
       <c r="F63" t="n">
-        <v>162.0</v>
+        <v>164.0</v>
       </c>
       <c r="G63" t="n">
         <v>31.0</v>
@@ -1862,7 +1862,7 @@
         <v>37</v>
       </c>
       <c r="F65" t="n">
-        <v>246.0</v>
+        <v>248.0</v>
       </c>
       <c r="G65" t="n">
         <v>115.0</v>
@@ -2252,7 +2252,7 @@
         <v>37</v>
       </c>
       <c r="F80" t="n">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="G80" t="n">
         <v>138.0</v>
@@ -2408,7 +2408,7 @@
         <v>38</v>
       </c>
       <c r="F86" t="n">
-        <v>84.0</v>
+        <v>85.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -3361,7 +3361,7 @@
         <v>150.0</v>
       </c>
       <c r="F16" t="n">
-        <v>25.0</v>
+        <v>28.0</v>
       </c>
       <c r="G16" t="n">
         <v>99.0</v>
@@ -3404,7 +3404,7 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="F18" t="n">
         <v>15.0</v>
@@ -3519,7 +3519,7 @@
         <v>36</v>
       </c>
       <c r="E23" t="n">
-        <v>125.0</v>
+        <v>130.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3611,7 +3611,7 @@
         <v>36</v>
       </c>
       <c r="E27" t="n">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -3851,7 +3851,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1352.0</v>
+        <v>1356.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3874,7 +3874,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1783.0</v>
+        <v>1787.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -3897,7 +3897,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>529.0</v>
+        <v>536.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3989,7 +3989,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>437.0</v>
+        <v>449.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4150,7 +4150,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9107.0</v>
+        <v>9108.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4173,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3184.0</v>
+        <v>3189.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4196,7 +4196,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6163.0</v>
+        <v>6168.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4242,7 +4242,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>7984.0</v>
+        <v>8004.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4265,7 +4265,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>3303.0</v>
+        <v>3321.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4288,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5033.0</v>
+        <v>5037.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>
@@ -4311,7 +4311,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1270.0</v>
+        <v>1272.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4541,7 +4541,7 @@
         <v>36</v>
       </c>
       <c r="E39" t="n">
-        <v>1275.0</v>
+        <v>1276.0</v>
       </c>
       <c r="F39" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -952,7 +952,7 @@
         <v>38</v>
       </c>
       <c r="F30" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -1030,7 +1030,7 @@
         <v>37</v>
       </c>
       <c r="F33" t="n">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1862,7 +1862,7 @@
         <v>37</v>
       </c>
       <c r="F65" t="n">
-        <v>248.0</v>
+        <v>249.0</v>
       </c>
       <c r="G65" t="n">
         <v>115.0</v>
@@ -2304,7 +2304,7 @@
         <v>39</v>
       </c>
       <c r="F82" t="n">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
       <c r="G82" t="n">
         <v>0.0</v>
@@ -3174,7 +3174,7 @@
         <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F8" t="n">
         <v>1.0</v>
@@ -4173,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3189.0</v>
+        <v>3190.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4196,7 +4196,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6168.0</v>
+        <v>6185.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4288,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5037.0</v>
+        <v>5043.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1186,7 +1186,7 @@
         <v>37</v>
       </c>
       <c r="F39" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -2928,7 +2928,7 @@
         <v>37</v>
       </c>
       <c r="F106" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="G106" t="n">
         <v>8.0</v>
@@ -3634,7 +3634,7 @@
         <v>30</v>
       </c>
       <c r="E28" t="n">
-        <v>13.0</v>
+        <v>18.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -4357,7 +4357,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>1888.0</v>
+        <v>1891.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4541,7 +4541,7 @@
         <v>36</v>
       </c>
       <c r="E39" t="n">
-        <v>1276.0</v>
+        <v>1279.0</v>
       </c>
       <c r="F39" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -250,7 +250,7 @@
         <v>38</v>
       </c>
       <c r="F3" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -952,7 +952,7 @@
         <v>38</v>
       </c>
       <c r="F30" t="n">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="G30" t="n">
         <v>0.0</v>
@@ -1472,7 +1472,7 @@
         <v>39</v>
       </c>
       <c r="F50" t="n">
-        <v>115.0</v>
+        <v>119.0</v>
       </c>
       <c r="G50" t="n">
         <v>7.0</v>
@@ -1550,7 +1550,7 @@
         <v>39</v>
       </c>
       <c r="F53" t="n">
-        <v>86.0</v>
+        <v>88.0</v>
       </c>
       <c r="G53" t="n">
         <v>3.0</v>
@@ -1628,7 +1628,7 @@
         <v>37</v>
       </c>
       <c r="F56" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1810,7 +1810,7 @@
         <v>38</v>
       </c>
       <c r="F63" t="n">
-        <v>164.0</v>
+        <v>166.0</v>
       </c>
       <c r="G63" t="n">
         <v>31.0</v>
@@ -1836,7 +1836,7 @@
         <v>39</v>
       </c>
       <c r="F64" t="n">
-        <v>180.0</v>
+        <v>181.0</v>
       </c>
       <c r="G64" t="n">
         <v>1.0</v>
@@ -3197,7 +3197,7 @@
         <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>26.0</v>
+        <v>29.0</v>
       </c>
       <c r="F9" t="n">
         <v>15.0</v>
@@ -3220,10 +3220,10 @@
         <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>186.0</v>
+        <v>189.0</v>
       </c>
       <c r="F10" t="n">
-        <v>103.0</v>
+        <v>107.0</v>
       </c>
       <c r="G10" t="n">
         <v>272.0</v>
@@ -3243,7 +3243,7 @@
         <v>20</v>
       </c>
       <c r="E11" t="n">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="F11" t="n">
         <v>49.0</v>
@@ -3289,7 +3289,7 @@
         <v>21</v>
       </c>
       <c r="E13" t="n">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="F13" t="n">
         <v>20.0</v>
@@ -3404,7 +3404,7 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="F18" t="n">
         <v>15.0</v>
@@ -3450,10 +3450,10 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>121.0</v>
+        <v>123.0</v>
       </c>
       <c r="F20" t="n">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="G20" t="n">
         <v>15.0</v>
@@ -3542,7 +3542,7 @@
         <v>17</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -3713,7 +3713,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>348.0</v>
+        <v>354.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3759,7 +3759,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>272.0</v>
+        <v>273.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3782,7 +3782,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>658.0</v>
+        <v>662.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3851,7 +3851,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1356.0</v>
+        <v>1360.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3874,7 +3874,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1787.0</v>
+        <v>1789.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -3897,7 +3897,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>536.0</v>
+        <v>547.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4035,7 +4035,7 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>436.0</v>
+        <v>446.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -4081,7 +4081,7 @@
         <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>1548.0</v>
+        <v>1555.0</v>
       </c>
       <c r="F19" t="n">
         <v>0.0</v>
@@ -4127,7 +4127,7 @@
         <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>621.0</v>
+        <v>622.0</v>
       </c>
       <c r="F21" t="n">
         <v>2.0</v>
@@ -4150,7 +4150,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9108.0</v>
+        <v>9132.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4173,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3190.0</v>
+        <v>3191.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4242,7 +4242,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8004.0</v>
+        <v>8011.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4265,7 +4265,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>3321.0</v>
+        <v>3323.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4288,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5043.0</v>
+        <v>5051.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>
@@ -4426,7 +4426,7 @@
         <v>18</v>
       </c>
       <c r="E34" t="n">
-        <v>58.0</v>
+        <v>60.0</v>
       </c>
       <c r="F34" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -874,7 +874,7 @@
         <v>38</v>
       </c>
       <c r="F27" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G27" t="n">
         <v>1.0</v>
@@ -900,7 +900,7 @@
         <v>39</v>
       </c>
       <c r="F28" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G28" t="n">
         <v>0.0</v>
@@ -1862,13 +1862,13 @@
         <v>37</v>
       </c>
       <c r="F65" t="n">
-        <v>249.0</v>
+        <v>250.0</v>
       </c>
       <c r="G65" t="n">
         <v>115.0</v>
       </c>
       <c r="H65" t="n">
-        <v>7.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="66">
@@ -1940,7 +1940,7 @@
         <v>37</v>
       </c>
       <c r="F68" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G68" t="n">
         <v>97.0</v>
@@ -2018,7 +2018,7 @@
         <v>37</v>
       </c>
       <c r="F71" t="n">
-        <v>157.0</v>
+        <v>159.0</v>
       </c>
       <c r="G71" t="n">
         <v>305.0</v>
@@ -2148,7 +2148,7 @@
         <v>39</v>
       </c>
       <c r="F76" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -3249,7 +3249,7 @@
         <v>49.0</v>
       </c>
       <c r="G11" t="n">
-        <v>18.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="12">
@@ -3358,10 +3358,10 @@
         <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>150.0</v>
+        <v>153.0</v>
       </c>
       <c r="F16" t="n">
-        <v>28.0</v>
+        <v>25.0</v>
       </c>
       <c r="G16" t="n">
         <v>99.0</v>
@@ -3450,7 +3450,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
       <c r="F20" t="n">
         <v>38.0</v>
@@ -4173,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3191.0</v>
+        <v>3195.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4219,7 +4219,7 @@
         <v>23</v>
       </c>
       <c r="E25" t="n">
-        <v>3395.0</v>
+        <v>3398.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -4242,7 +4242,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8011.0</v>
+        <v>8019.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -978,7 +978,7 @@
         <v>39</v>
       </c>
       <c r="F31" t="n">
-        <v>50.0</v>
+        <v>52.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -1030,7 +1030,7 @@
         <v>37</v>
       </c>
       <c r="F33" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G33" t="n">
         <v>0.0</v>
@@ -1056,7 +1056,7 @@
         <v>38</v>
       </c>
       <c r="F34" t="n">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1238,7 +1238,7 @@
         <v>39</v>
       </c>
       <c r="F41" t="n">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1371,7 +1371,7 @@
         <v>13.0</v>
       </c>
       <c r="G46" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H46" t="n">
         <v>0.0</v>
@@ -2278,7 +2278,7 @@
         <v>38</v>
       </c>
       <c r="F81" t="n">
-        <v>102.0</v>
+        <v>103.0</v>
       </c>
       <c r="G81" t="n">
         <v>135.0</v>
@@ -3450,7 +3450,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>124.0</v>
+        <v>128.0</v>
       </c>
       <c r="F20" t="n">
         <v>38.0</v>
@@ -3634,13 +3634,13 @@
         <v>30</v>
       </c>
       <c r="E28" t="n">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
       </c>
       <c r="G28" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
   </sheetData>
@@ -3897,7 +3897,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>547.0</v>
+        <v>561.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3989,7 +3989,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>449.0</v>
+        <v>454.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4150,7 +4150,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9132.0</v>
+        <v>9170.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4173,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3195.0</v>
+        <v>3229.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4196,7 +4196,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6185.0</v>
+        <v>6188.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4242,7 +4242,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8019.0</v>
+        <v>8028.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4288,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5051.0</v>
+        <v>5064.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>
@@ -4311,7 +4311,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1272.0</v>
+        <v>1279.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4357,7 +4357,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>1891.0</v>
+        <v>1904.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4541,7 +4541,7 @@
         <v>36</v>
       </c>
       <c r="E39" t="n">
-        <v>1279.0</v>
+        <v>1309.0</v>
       </c>
       <c r="F39" t="n">
         <v>0.0</v>
@@ -4564,13 +4564,13 @@
         <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>1146.0</v>
+        <v>1147.0</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>
       </c>
       <c r="G40" t="n">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
     </row>
   </sheetData>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1160,7 +1160,7 @@
         <v>39</v>
       </c>
       <c r="F38" t="n">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="G38" t="n">
         <v>0.0</v>
@@ -1706,7 +1706,7 @@
         <v>37</v>
       </c>
       <c r="F59" t="n">
-        <v>1394.0</v>
+        <v>1395.0</v>
       </c>
       <c r="G59" t="n">
         <v>701.0</v>
@@ -2980,7 +2980,7 @@
         <v>39</v>
       </c>
       <c r="F108" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -3542,7 +3542,7 @@
         <v>17</v>
       </c>
       <c r="E24" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -3690,7 +3690,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>143.0</v>
+        <v>144.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -3713,7 +3713,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>354.0</v>
+        <v>357.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3736,7 +3736,7 @@
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>148.0</v>
+        <v>150.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -3759,7 +3759,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>273.0</v>
+        <v>274.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3782,7 +3782,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>662.0</v>
+        <v>672.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3851,7 +3851,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1360.0</v>
+        <v>1362.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3874,7 +3874,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1789.0</v>
+        <v>1806.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -3897,7 +3897,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>561.0</v>
+        <v>562.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3989,7 +3989,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>454.0</v>
+        <v>456.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4035,7 +4035,7 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>446.0</v>
+        <v>452.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -4058,7 +4058,7 @@
         <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>3501.0</v>
+        <v>3505.0</v>
       </c>
       <c r="F18" t="n">
         <v>2.0</v>
@@ -4081,7 +4081,7 @@
         <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>1555.0</v>
+        <v>1563.0</v>
       </c>
       <c r="F19" t="n">
         <v>0.0</v>
@@ -4127,7 +4127,7 @@
         <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>622.0</v>
+        <v>641.0</v>
       </c>
       <c r="F21" t="n">
         <v>2.0</v>
@@ -4150,7 +4150,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9170.0</v>
+        <v>9183.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4242,13 +4242,13 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8028.0</v>
+        <v>8038.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
       </c>
       <c r="G26" t="n">
-        <v>213.0</v>
+        <v>214.0</v>
       </c>
     </row>
     <row r="27">
@@ -4265,7 +4265,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>3323.0</v>
+        <v>3351.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4288,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5064.0</v>
+        <v>5065.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>
@@ -4426,7 +4426,7 @@
         <v>18</v>
       </c>
       <c r="E34" t="n">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="F34" t="n">
         <v>0.0</v>
@@ -4472,7 +4472,7 @@
         <v>21</v>
       </c>
       <c r="E36" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="F36" t="n">
         <v>0.0</v>
@@ -4564,7 +4564,7 @@
         <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>1147.0</v>
+        <v>1148.0</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1706,7 +1706,7 @@
         <v>37</v>
       </c>
       <c r="F59" t="n">
-        <v>1395.0</v>
+        <v>1396.0</v>
       </c>
       <c r="G59" t="n">
         <v>701.0</v>
@@ -1888,7 +1888,7 @@
         <v>38</v>
       </c>
       <c r="F66" t="n">
-        <v>209.0</v>
+        <v>210.0</v>
       </c>
       <c r="G66" t="n">
         <v>53.0</v>
@@ -2018,7 +2018,7 @@
         <v>37</v>
       </c>
       <c r="F71" t="n">
-        <v>159.0</v>
+        <v>160.0</v>
       </c>
       <c r="G71" t="n">
         <v>305.0</v>
@@ -2070,7 +2070,7 @@
         <v>39</v>
       </c>
       <c r="F73" t="n">
-        <v>295.0</v>
+        <v>297.0</v>
       </c>
       <c r="G73" t="n">
         <v>19.0</v>
@@ -3450,7 +3450,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>128.0</v>
+        <v>131.0</v>
       </c>
       <c r="F20" t="n">
         <v>38.0</v>
@@ -3805,7 +3805,7 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>1202.0</v>
+        <v>1250.0</v>
       </c>
       <c r="F7" t="n">
         <v>0.0</v>
@@ -3851,7 +3851,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1362.0</v>
+        <v>1365.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -4150,7 +4150,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9183.0</v>
+        <v>9190.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4173,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3229.0</v>
+        <v>3238.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4196,7 +4196,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6188.0</v>
+        <v>6259.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4288,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5065.0</v>
+        <v>5067.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>
@@ -4357,7 +4357,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>1904.0</v>
+        <v>1907.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4564,7 +4564,7 @@
         <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>1148.0</v>
+        <v>1151.0</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1186,7 +1186,7 @@
         <v>37</v>
       </c>
       <c r="F39" t="n">
-        <v>6.0</v>
+        <v>12.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -4357,7 +4357,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>1907.0</v>
+        <v>1925.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4541,7 +4541,7 @@
         <v>36</v>
       </c>
       <c r="E39" t="n">
-        <v>1309.0</v>
+        <v>1313.0</v>
       </c>
       <c r="F39" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1862,7 +1862,7 @@
         <v>37</v>
       </c>
       <c r="F65" t="n">
-        <v>250.0</v>
+        <v>252.0</v>
       </c>
       <c r="G65" t="n">
         <v>115.0</v>
@@ -3358,7 +3358,7 @@
         <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>153.0</v>
+        <v>156.0</v>
       </c>
       <c r="F16" t="n">
         <v>25.0</v>
@@ -3805,7 +3805,7 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>1250.0</v>
+        <v>1251.0</v>
       </c>
       <c r="F7" t="n">
         <v>0.0</v>
@@ -3874,7 +3874,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1806.0</v>
+        <v>1808.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -4150,7 +4150,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9190.0</v>
+        <v>9234.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4173,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3238.0</v>
+        <v>3243.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4196,7 +4196,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6259.0</v>
+        <v>6278.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4242,7 +4242,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8038.0</v>
+        <v>8046.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4265,7 +4265,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>3351.0</v>
+        <v>3352.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4288,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5067.0</v>
+        <v>5069.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -718,7 +718,7 @@
         <v>38</v>
       </c>
       <c r="F21" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="G21" t="n">
         <v>1.0</v>
@@ -978,7 +978,7 @@
         <v>39</v>
       </c>
       <c r="F31" t="n">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="G31" t="n">
         <v>0.0</v>
@@ -1420,7 +1420,7 @@
         <v>37</v>
       </c>
       <c r="F48" t="n">
-        <v>56.0</v>
+        <v>58.0</v>
       </c>
       <c r="G48" t="n">
         <v>69.0</v>
@@ -1550,7 +1550,7 @@
         <v>39</v>
       </c>
       <c r="F53" t="n">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
       <c r="G53" t="n">
         <v>3.0</v>
@@ -2278,7 +2278,7 @@
         <v>38</v>
       </c>
       <c r="F81" t="n">
-        <v>103.0</v>
+        <v>104.0</v>
       </c>
       <c r="G81" t="n">
         <v>135.0</v>
@@ -3223,7 +3223,7 @@
         <v>189.0</v>
       </c>
       <c r="F10" t="n">
-        <v>107.0</v>
+        <v>111.0</v>
       </c>
       <c r="G10" t="n">
         <v>272.0</v>
@@ -3246,7 +3246,7 @@
         <v>47.0</v>
       </c>
       <c r="F11" t="n">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="G11" t="n">
         <v>20.0</v>
@@ -3542,10 +3542,10 @@
         <v>17</v>
       </c>
       <c r="E24" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G24" t="n">
         <v>2.0</v>
@@ -3713,7 +3713,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>357.0</v>
+        <v>362.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3759,7 +3759,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>274.0</v>
+        <v>275.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3782,7 +3782,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>672.0</v>
+        <v>686.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -4035,7 +4035,7 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>452.0</v>
+        <v>455.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -4058,7 +4058,7 @@
         <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>3505.0</v>
+        <v>3510.0</v>
       </c>
       <c r="F18" t="n">
         <v>2.0</v>
@@ -4081,13 +4081,13 @@
         <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>1563.0</v>
+        <v>1565.0</v>
       </c>
       <c r="F19" t="n">
         <v>0.0</v>
       </c>
       <c r="G19" t="n">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
     </row>
     <row r="20">
@@ -4127,7 +4127,7 @@
         <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>641.0</v>
+        <v>648.0</v>
       </c>
       <c r="F21" t="n">
         <v>2.0</v>
@@ -4219,7 +4219,7 @@
         <v>23</v>
       </c>
       <c r="E25" t="n">
-        <v>3398.0</v>
+        <v>3399.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -4242,7 +4242,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8046.0</v>
+        <v>8076.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4288,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5069.0</v>
+        <v>5071.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>
@@ -4311,7 +4311,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1279.0</v>
+        <v>1280.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4403,7 +4403,7 @@
         <v>17</v>
       </c>
       <c r="E33" t="n">
-        <v>111.0</v>
+        <v>119.0</v>
       </c>
       <c r="F33" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1056,7 +1056,7 @@
         <v>38</v>
       </c>
       <c r="F34" t="n">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="G34" t="n">
         <v>0.0</v>
@@ -1836,7 +1836,7 @@
         <v>39</v>
       </c>
       <c r="F64" t="n">
-        <v>181.0</v>
+        <v>182.0</v>
       </c>
       <c r="G64" t="n">
         <v>1.0</v>
@@ -2408,7 +2408,7 @@
         <v>38</v>
       </c>
       <c r="F86" t="n">
-        <v>85.0</v>
+        <v>86.0</v>
       </c>
       <c r="G86" t="n">
         <v>0.0</v>
@@ -2980,7 +2980,7 @@
         <v>39</v>
       </c>
       <c r="F108" t="n">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="G108" t="n">
         <v>0.0</v>
@@ -3174,7 +3174,7 @@
         <v>26</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F8" t="n">
         <v>1.0</v>
@@ -3450,7 +3450,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>131.0</v>
+        <v>132.0</v>
       </c>
       <c r="F20" t="n">
         <v>38.0</v>
@@ -3805,7 +3805,7 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>1251.0</v>
+        <v>1289.0</v>
       </c>
       <c r="F7" t="n">
         <v>0.0</v>
@@ -3874,7 +3874,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1808.0</v>
+        <v>1821.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -3897,7 +3897,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>562.0</v>
+        <v>578.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3966,7 +3966,7 @@
         <v>29</v>
       </c>
       <c r="E14" t="n">
-        <v>180.0</v>
+        <v>181.0</v>
       </c>
       <c r="F14" t="n">
         <v>0.0</v>
@@ -3989,7 +3989,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>456.0</v>
+        <v>465.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4012,7 +4012,7 @@
         <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>59.0</v>
+        <v>69.0</v>
       </c>
       <c r="F16" t="n">
         <v>0.0</v>
@@ -4150,7 +4150,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9234.0</v>
+        <v>9298.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4173,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3243.0</v>
+        <v>3278.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4196,7 +4196,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6278.0</v>
+        <v>6344.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4265,7 +4265,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>3352.0</v>
+        <v>3382.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4288,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5071.0</v>
+        <v>5114.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>
@@ -4311,7 +4311,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1280.0</v>
+        <v>1284.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4357,7 +4357,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>1925.0</v>
+        <v>1975.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4541,7 +4541,7 @@
         <v>36</v>
       </c>
       <c r="E39" t="n">
-        <v>1313.0</v>
+        <v>1342.0</v>
       </c>
       <c r="F39" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1446,7 +1446,7 @@
         <v>38</v>
       </c>
       <c r="F49" t="n">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="G49" t="n">
         <v>35.0</v>
@@ -2044,7 +2044,7 @@
         <v>38</v>
       </c>
       <c r="F72" t="n">
-        <v>201.0</v>
+        <v>202.0</v>
       </c>
       <c r="G72" t="n">
         <v>141.0</v>
@@ -2148,7 +2148,7 @@
         <v>39</v>
       </c>
       <c r="F76" t="n">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="G76" t="n">
         <v>0.0</v>
@@ -3223,7 +3223,7 @@
         <v>189.0</v>
       </c>
       <c r="F10" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="G10" t="n">
         <v>272.0</v>
@@ -3450,7 +3450,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>132.0</v>
+        <v>133.0</v>
       </c>
       <c r="F20" t="n">
         <v>38.0</v>
@@ -3519,7 +3519,7 @@
         <v>36</v>
       </c>
       <c r="E23" t="n">
-        <v>130.0</v>
+        <v>131.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -3542,7 +3542,7 @@
         <v>17</v>
       </c>
       <c r="E24" t="n">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -3611,7 +3611,7 @@
         <v>36</v>
       </c>
       <c r="E27" t="n">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
@@ -3851,7 +3851,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1365.0</v>
+        <v>1373.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3874,7 +3874,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1821.0</v>
+        <v>1822.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -3897,7 +3897,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>578.0</v>
+        <v>580.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4058,7 +4058,7 @@
         <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>3510.0</v>
+        <v>3511.0</v>
       </c>
       <c r="F18" t="n">
         <v>2.0</v>
@@ -4081,7 +4081,7 @@
         <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>1565.0</v>
+        <v>1566.0</v>
       </c>
       <c r="F19" t="n">
         <v>0.0</v>
@@ -4127,7 +4127,7 @@
         <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>648.0</v>
+        <v>650.0</v>
       </c>
       <c r="F21" t="n">
         <v>2.0</v>
@@ -4242,7 +4242,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8076.0</v>
+        <v>8102.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4288,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5114.0</v>
+        <v>5116.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>
@@ -4311,7 +4311,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1284.0</v>
+        <v>1289.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4357,7 +4357,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>1975.0</v>
+        <v>1978.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4564,7 +4564,7 @@
         <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>1151.0</v>
+        <v>1157.0</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1004,7 +1004,7 @@
         <v>39</v>
       </c>
       <c r="F32" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="G32" t="n">
         <v>0.0</v>
@@ -1108,7 +1108,7 @@
         <v>37</v>
       </c>
       <c r="F36" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G36" t="n">
         <v>0.0</v>
@@ -2177,7 +2177,7 @@
         <v>46.0</v>
       </c>
       <c r="G77" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H77" t="n">
         <v>0.0</v>
@@ -3450,7 +3450,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>133.0</v>
+        <v>138.0</v>
       </c>
       <c r="F20" t="n">
         <v>38.0</v>
@@ -4173,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3278.0</v>
+        <v>3286.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4242,7 +4242,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8102.0</v>
+        <v>8114.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4265,7 +4265,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>3382.0</v>
+        <v>3384.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4288,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5116.0</v>
+        <v>5119.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>
@@ -4357,7 +4357,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>1978.0</v>
+        <v>1979.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -2876,7 +2876,7 @@
         <v>38</v>
       </c>
       <c r="F104" t="n">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
@@ -3502,7 +3502,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
     </row>
     <row r="23">
@@ -4012,7 +4012,7 @@
         <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>69.0</v>
+        <v>71.0</v>
       </c>
       <c r="F16" t="n">
         <v>0.0</v>
@@ -4357,7 +4357,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>1979.0</v>
+        <v>1988.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4541,7 +4541,7 @@
         <v>36</v>
       </c>
       <c r="E39" t="n">
-        <v>1342.0</v>
+        <v>1349.0</v>
       </c>
       <c r="F39" t="n">
         <v>0.0</v>
@@ -4564,7 +4564,7 @@
         <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>1157.0</v>
+        <v>1159.0</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -640,13 +640,13 @@
         <v>38</v>
       </c>
       <c r="F18" t="n">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="G18" t="n">
         <v>0.0</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="19">
@@ -3358,10 +3358,10 @@
         <v>22</v>
       </c>
       <c r="E16" t="n">
-        <v>156.0</v>
+        <v>160.0</v>
       </c>
       <c r="F16" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G16" t="n">
         <v>99.0</v>
@@ -3805,7 +3805,7 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>1289.0</v>
+        <v>1325.0</v>
       </c>
       <c r="F7" t="n">
         <v>0.0</v>
@@ -3851,7 +3851,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1373.0</v>
+        <v>1374.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3874,7 +3874,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1822.0</v>
+        <v>1824.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -3897,7 +3897,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>580.0</v>
+        <v>601.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4150,7 +4150,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9298.0</v>
+        <v>9353.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4173,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3286.0</v>
+        <v>3293.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4196,7 +4196,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6344.0</v>
+        <v>6402.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4242,7 +4242,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8114.0</v>
+        <v>8119.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4265,7 +4265,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>3384.0</v>
+        <v>3391.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4288,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5119.0</v>
+        <v>5144.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>
@@ -4357,7 +4357,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>1988.0</v>
+        <v>1989.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -2122,7 +2122,7 @@
         <v>38</v>
       </c>
       <c r="F75" t="n">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="G75" t="n">
         <v>9.0</v>
@@ -3364,7 +3364,7 @@
         <v>26.0</v>
       </c>
       <c r="G16" t="n">
-        <v>99.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="17">
@@ -3450,7 +3450,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>138.0</v>
+        <v>139.0</v>
       </c>
       <c r="F20" t="n">
         <v>38.0</v>
@@ -3828,7 +3828,7 @@
         <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>669.0</v>
+        <v>677.0</v>
       </c>
       <c r="F8" t="n">
         <v>0.0</v>
@@ -3897,7 +3897,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>601.0</v>
+        <v>603.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -4219,7 +4219,7 @@
         <v>23</v>
       </c>
       <c r="E25" t="n">
-        <v>3399.0</v>
+        <v>3405.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -4242,7 +4242,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8119.0</v>
+        <v>8133.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4265,7 +4265,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>3391.0</v>
+        <v>3395.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -926,7 +926,7 @@
         <v>37</v>
       </c>
       <c r="F29" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="G29" t="n">
         <v>0.0</v>
@@ -1498,7 +1498,7 @@
         <v>37</v>
       </c>
       <c r="F51" t="n">
-        <v>32.0</v>
+        <v>35.0</v>
       </c>
       <c r="G51" t="n">
         <v>144.0</v>
@@ -3226,7 +3226,7 @@
         <v>112.0</v>
       </c>
       <c r="G10" t="n">
-        <v>272.0</v>
+        <v>273.0</v>
       </c>
     </row>
     <row r="11">
@@ -3634,7 +3634,7 @@
         <v>30</v>
       </c>
       <c r="E28" t="n">
-        <v>19.0</v>
+        <v>29.0</v>
       </c>
       <c r="F28" t="n">
         <v>0.0</v>
@@ -3805,7 +3805,7 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>1325.0</v>
+        <v>1337.0</v>
       </c>
       <c r="F7" t="n">
         <v>0.0</v>
@@ -3851,7 +3851,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1374.0</v>
+        <v>1376.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3874,7 +3874,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1824.0</v>
+        <v>1839.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -3897,7 +3897,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>603.0</v>
+        <v>619.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3989,7 +3989,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>465.0</v>
+        <v>468.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4012,7 +4012,7 @@
         <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>71.0</v>
+        <v>88.0</v>
       </c>
       <c r="F16" t="n">
         <v>0.0</v>
@@ -4150,7 +4150,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9353.0</v>
+        <v>9387.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4173,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3293.0</v>
+        <v>3333.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4196,7 +4196,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6402.0</v>
+        <v>6457.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4242,7 +4242,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8133.0</v>
+        <v>8164.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4265,7 +4265,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>3395.0</v>
+        <v>3404.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4288,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5144.0</v>
+        <v>5189.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>
@@ -4357,7 +4357,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>1989.0</v>
+        <v>2008.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4541,7 +4541,7 @@
         <v>36</v>
       </c>
       <c r="E39" t="n">
-        <v>1349.0</v>
+        <v>1369.0</v>
       </c>
       <c r="F39" t="n">
         <v>0.0</v>
@@ -4564,7 +4564,7 @@
         <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>1159.0</v>
+        <v>1162.0</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1706,7 +1706,7 @@
         <v>37</v>
       </c>
       <c r="F59" t="n">
-        <v>1396.0</v>
+        <v>1398.0</v>
       </c>
       <c r="G59" t="n">
         <v>701.0</v>
@@ -1758,7 +1758,7 @@
         <v>39</v>
       </c>
       <c r="F61" t="n">
-        <v>269.0</v>
+        <v>270.0</v>
       </c>
       <c r="G61" t="n">
         <v>16.0</v>
@@ -2252,7 +2252,7 @@
         <v>37</v>
       </c>
       <c r="F80" t="n">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="G80" t="n">
         <v>138.0</v>
@@ -2278,7 +2278,7 @@
         <v>38</v>
       </c>
       <c r="F81" t="n">
-        <v>104.0</v>
+        <v>105.0</v>
       </c>
       <c r="G81" t="n">
         <v>135.0</v>
@@ -3197,7 +3197,7 @@
         <v>18</v>
       </c>
       <c r="E9" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="F9" t="n">
         <v>15.0</v>
@@ -3220,10 +3220,10 @@
         <v>19</v>
       </c>
       <c r="E10" t="n">
-        <v>189.0</v>
+        <v>190.0</v>
       </c>
       <c r="F10" t="n">
-        <v>112.0</v>
+        <v>113.0</v>
       </c>
       <c r="G10" t="n">
         <v>273.0</v>
@@ -3289,7 +3289,7 @@
         <v>21</v>
       </c>
       <c r="E13" t="n">
-        <v>25.0</v>
+        <v>29.0</v>
       </c>
       <c r="F13" t="n">
         <v>20.0</v>
@@ -3473,13 +3473,13 @@
         <v>28</v>
       </c>
       <c r="E21" t="n">
-        <v>195.0</v>
+        <v>201.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
     </row>
     <row r="22">
@@ -3502,7 +3502,7 @@
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>123.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="23">
@@ -3542,7 +3542,7 @@
         <v>17</v>
       </c>
       <c r="E24" t="n">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="F24" t="n">
         <v>1.0</v>
@@ -3690,7 +3690,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>144.0</v>
+        <v>145.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -3713,7 +3713,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>362.0</v>
+        <v>384.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3736,7 +3736,7 @@
         <v>19</v>
       </c>
       <c r="E4" t="n">
-        <v>150.0</v>
+        <v>153.0</v>
       </c>
       <c r="F4" t="n">
         <v>1.0</v>
@@ -3759,7 +3759,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>275.0</v>
+        <v>278.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3782,7 +3782,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>686.0</v>
+        <v>707.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3805,7 +3805,7 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>1337.0</v>
+        <v>1338.0</v>
       </c>
       <c r="F7" t="n">
         <v>0.0</v>
@@ -3943,7 +3943,7 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>110.0</v>
+        <v>111.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -3989,7 +3989,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>468.0</v>
+        <v>470.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4012,7 +4012,7 @@
         <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>88.0</v>
+        <v>89.0</v>
       </c>
       <c r="F16" t="n">
         <v>0.0</v>
@@ -4035,7 +4035,7 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>455.0</v>
+        <v>457.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -4058,7 +4058,7 @@
         <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>3511.0</v>
+        <v>3566.0</v>
       </c>
       <c r="F18" t="n">
         <v>2.0</v>
@@ -4081,7 +4081,7 @@
         <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>1566.0</v>
+        <v>1567.0</v>
       </c>
       <c r="F19" t="n">
         <v>0.0</v>
@@ -4127,7 +4127,7 @@
         <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>650.0</v>
+        <v>659.0</v>
       </c>
       <c r="F21" t="n">
         <v>2.0</v>
@@ -4150,13 +4150,13 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9387.0</v>
+        <v>9394.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
       </c>
       <c r="G22" t="n">
-        <v>187.0</v>
+        <v>188.0</v>
       </c>
     </row>
     <row r="23">
@@ -4173,7 +4173,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3333.0</v>
+        <v>3335.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4242,7 +4242,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8164.0</v>
+        <v>8165.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4265,7 +4265,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>3404.0</v>
+        <v>3406.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4311,7 +4311,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1289.0</v>
+        <v>1306.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4357,7 +4357,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>2008.0</v>
+        <v>2010.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4541,7 +4541,7 @@
         <v>36</v>
       </c>
       <c r="E39" t="n">
-        <v>1369.0</v>
+        <v>1370.0</v>
       </c>
       <c r="F39" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1628,7 +1628,7 @@
         <v>37</v>
       </c>
       <c r="F56" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="G56" t="n">
         <v>0.0</v>
@@ -1888,7 +1888,7 @@
         <v>38</v>
       </c>
       <c r="F66" t="n">
-        <v>210.0</v>
+        <v>215.0</v>
       </c>
       <c r="G66" t="n">
         <v>53.0</v>
@@ -3289,7 +3289,7 @@
         <v>21</v>
       </c>
       <c r="E13" t="n">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="F13" t="n">
         <v>20.0</v>
@@ -3450,7 +3450,7 @@
         <v>26</v>
       </c>
       <c r="E20" t="n">
-        <v>139.0</v>
+        <v>140.0</v>
       </c>
       <c r="F20" t="n">
         <v>38.0</v>
@@ -3851,7 +3851,7 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1376.0</v>
+        <v>1378.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
@@ -3874,7 +3874,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1839.0</v>
+        <v>1841.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -4196,7 +4196,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6457.0</v>
+        <v>6458.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4242,7 +4242,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8165.0</v>
+        <v>8183.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4288,7 +4288,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5189.0</v>
+        <v>5192.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -3226,7 +3226,7 @@
         <v>113.0</v>
       </c>
       <c r="G10" t="n">
-        <v>273.0</v>
+        <v>274.0</v>
       </c>
     </row>
     <row r="11">
@@ -3943,7 +3943,7 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>111.0</v>
+        <v>112.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -4012,7 +4012,7 @@
         <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>89.0</v>
+        <v>92.0</v>
       </c>
       <c r="F16" t="n">
         <v>0.0</v>
@@ -4311,7 +4311,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1306.0</v>
+        <v>1310.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4357,7 +4357,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>2010.0</v>
+        <v>2011.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4541,7 +4541,7 @@
         <v>36</v>
       </c>
       <c r="E39" t="n">
-        <v>1370.0</v>
+        <v>1380.0</v>
       </c>
       <c r="F39" t="n">
         <v>0.0</v>
@@ -4564,7 +4564,7 @@
         <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>1162.0</v>
+        <v>1176.0</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="821" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="40">
   <si>
     <t>Area</t>
   </si>
@@ -34,10 +34,10 @@
     <t>Negative</t>
   </si>
   <si>
-    <t>Positive</t>
+    <t>Not performed</t>
   </si>
   <si>
-    <t>Not performed</t>
+    <t>Positive</t>
   </si>
   <si>
     <t>Pl</t>
@@ -458,7 +458,7 @@
         <v>37</v>
       </c>
       <c r="F11" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="G11" t="n">
         <v>0.0</v>
@@ -484,10 +484,10 @@
         <v>38</v>
       </c>
       <c r="F12" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G12" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H12" t="n">
         <v>0.0</v>
@@ -510,7 +510,7 @@
         <v>39</v>
       </c>
       <c r="F13" t="n">
-        <v>33.0</v>
+        <v>35.0</v>
       </c>
       <c r="G13" t="n">
         <v>0.0</v>
@@ -562,7 +562,7 @@
         <v>38</v>
       </c>
       <c r="F15" t="n">
-        <v>27.0</v>
+        <v>21.0</v>
       </c>
       <c r="G15" t="n">
         <v>0.0</v>
@@ -588,7 +588,7 @@
         <v>39</v>
       </c>
       <c r="F16" t="n">
-        <v>80.0</v>
+        <v>69.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -643,10 +643,10 @@
         <v>22.0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H18" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="19">
@@ -692,13 +692,13 @@
         <v>37</v>
       </c>
       <c r="F20" t="n">
-        <v>14.0</v>
+        <v>11.0</v>
       </c>
       <c r="G20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H20" t="n">
         <v>4.0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="21">
@@ -718,13 +718,13 @@
         <v>38</v>
       </c>
       <c r="F21" t="n">
-        <v>43.0</v>
+        <v>31.0</v>
       </c>
       <c r="G21" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="22">
@@ -744,13 +744,13 @@
         <v>39</v>
       </c>
       <c r="F22" t="n">
-        <v>47.0</v>
+        <v>55.0</v>
       </c>
       <c r="G22" t="n">
         <v>0.0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="23">
@@ -770,7 +770,7 @@
         <v>37</v>
       </c>
       <c r="F23" t="n">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="G23" t="n">
         <v>0.0</v>
@@ -796,13 +796,13 @@
         <v>38</v>
       </c>
       <c r="F24" t="n">
-        <v>15.0</v>
+        <v>17.0</v>
       </c>
       <c r="G24" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H24" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="25">
@@ -828,7 +828,7 @@
         <v>0.0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="26">
@@ -877,10 +877,10 @@
         <v>28.0</v>
       </c>
       <c r="G27" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H27" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="28">
@@ -900,7 +900,7 @@
         <v>39</v>
       </c>
       <c r="F28" t="n">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="G28" t="n">
         <v>0.0</v>
@@ -929,10 +929,10 @@
         <v>12.0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H29" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="30">
@@ -955,10 +955,10 @@
         <v>29.0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H30" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="31">
@@ -1137,10 +1137,10 @@
         <v>17.0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H37" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="38">
@@ -1163,10 +1163,10 @@
         <v>25.0</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H38" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="39">
@@ -1186,7 +1186,7 @@
         <v>37</v>
       </c>
       <c r="F39" t="n">
-        <v>12.0</v>
+        <v>11.0</v>
       </c>
       <c r="G39" t="n">
         <v>0.0</v>
@@ -1212,7 +1212,7 @@
         <v>38</v>
       </c>
       <c r="F40" t="n">
-        <v>25.0</v>
+        <v>22.0</v>
       </c>
       <c r="G40" t="n">
         <v>0.0</v>
@@ -1238,7 +1238,7 @@
         <v>39</v>
       </c>
       <c r="F41" t="n">
-        <v>33.0</v>
+        <v>18.0</v>
       </c>
       <c r="G41" t="n">
         <v>0.0</v>
@@ -1345,10 +1345,10 @@
         <v>8.0</v>
       </c>
       <c r="G45" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H45" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="46">
@@ -1371,10 +1371,10 @@
         <v>13.0</v>
       </c>
       <c r="G46" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H46" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="47">
@@ -1423,10 +1423,10 @@
         <v>58.0</v>
       </c>
       <c r="G48" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H48" t="n">
         <v>69.0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="49">
@@ -1449,10 +1449,10 @@
         <v>44.0</v>
       </c>
       <c r="G49" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H49" t="n">
         <v>35.0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="50">
@@ -1475,10 +1475,10 @@
         <v>119.0</v>
       </c>
       <c r="G50" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H50" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="51">
@@ -1498,13 +1498,13 @@
         <v>37</v>
       </c>
       <c r="F51" t="n">
-        <v>35.0</v>
+        <v>33.0</v>
       </c>
       <c r="G51" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H51" t="n">
         <v>144.0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="52">
@@ -1524,13 +1524,13 @@
         <v>38</v>
       </c>
       <c r="F52" t="n">
-        <v>42.0</v>
+        <v>38.0</v>
       </c>
       <c r="G52" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H52" t="n">
         <v>27.0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>2.0</v>
       </c>
     </row>
     <row r="53">
@@ -1550,13 +1550,13 @@
         <v>39</v>
       </c>
       <c r="F53" t="n">
-        <v>89.0</v>
+        <v>80.0</v>
       </c>
       <c r="G53" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H53" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="54">
@@ -1579,10 +1579,10 @@
         <v>0.0</v>
       </c>
       <c r="G54" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H54" t="n">
         <v>47.0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="55">
@@ -1605,10 +1605,10 @@
         <v>0.0</v>
       </c>
       <c r="G55" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H55" t="n">
         <v>7.0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="56">
@@ -1709,10 +1709,10 @@
         <v>1398.0</v>
       </c>
       <c r="G59" t="n">
+        <v>92.0</v>
+      </c>
+      <c r="H59" t="n">
         <v>701.0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>92.0</v>
       </c>
     </row>
     <row r="60">
@@ -1735,10 +1735,10 @@
         <v>261.0</v>
       </c>
       <c r="G60" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="H60" t="n">
         <v>70.0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>25.0</v>
       </c>
     </row>
     <row r="61">
@@ -1761,10 +1761,10 @@
         <v>270.0</v>
       </c>
       <c r="G61" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="H61" t="n">
         <v>16.0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>8.0</v>
       </c>
     </row>
     <row r="62">
@@ -1787,10 +1787,10 @@
         <v>86.0</v>
       </c>
       <c r="G62" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H62" t="n">
         <v>9.0</v>
-      </c>
-      <c r="H62" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="63">
@@ -1813,10 +1813,10 @@
         <v>166.0</v>
       </c>
       <c r="G63" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="H63" t="n">
         <v>31.0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>11.0</v>
       </c>
     </row>
     <row r="64">
@@ -1839,10 +1839,10 @@
         <v>182.0</v>
       </c>
       <c r="G64" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="H64" t="n">
         <v>1.0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>4.0</v>
       </c>
     </row>
     <row r="65">
@@ -1865,10 +1865,10 @@
         <v>252.0</v>
       </c>
       <c r="G65" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="H65" t="n">
         <v>115.0</v>
-      </c>
-      <c r="H65" t="n">
-        <v>6.0</v>
       </c>
     </row>
     <row r="66">
@@ -1891,10 +1891,10 @@
         <v>215.0</v>
       </c>
       <c r="G66" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="H66" t="n">
         <v>53.0</v>
-      </c>
-      <c r="H66" t="n">
-        <v>13.0</v>
       </c>
     </row>
     <row r="67">
@@ -1917,10 +1917,10 @@
         <v>122.0</v>
       </c>
       <c r="G67" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H67" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H67" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="68">
@@ -1940,13 +1940,13 @@
         <v>37</v>
       </c>
       <c r="F68" t="n">
-        <v>44.0</v>
+        <v>37.0</v>
       </c>
       <c r="G68" t="n">
-        <v>97.0</v>
+        <v>0.0</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0</v>
+        <v>94.0</v>
       </c>
     </row>
     <row r="69">
@@ -1966,13 +1966,13 @@
         <v>38</v>
       </c>
       <c r="F69" t="n">
-        <v>84.0</v>
+        <v>62.0</v>
       </c>
       <c r="G69" t="n">
-        <v>21.0</v>
+        <v>0.0</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="70">
@@ -1992,13 +1992,13 @@
         <v>39</v>
       </c>
       <c r="F70" t="n">
-        <v>128.0</v>
+        <v>90.0</v>
       </c>
       <c r="G70" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H70" t="n">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="71">
@@ -2021,10 +2021,10 @@
         <v>160.0</v>
       </c>
       <c r="G71" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H71" t="n">
         <v>305.0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="72">
@@ -2044,13 +2044,13 @@
         <v>38</v>
       </c>
       <c r="F72" t="n">
-        <v>202.0</v>
+        <v>200.0</v>
       </c>
       <c r="G72" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H72" t="n">
         <v>141.0</v>
-      </c>
-      <c r="H72" t="n">
-        <v>3.0</v>
       </c>
     </row>
     <row r="73">
@@ -2073,10 +2073,10 @@
         <v>297.0</v>
       </c>
       <c r="G73" t="n">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0</v>
+        <v>18.0</v>
       </c>
     </row>
     <row r="74">
@@ -2099,10 +2099,10 @@
         <v>80.0</v>
       </c>
       <c r="G74" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H74" t="n">
         <v>3.0</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="75">
@@ -2125,10 +2125,10 @@
         <v>72.0</v>
       </c>
       <c r="G75" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H75" t="n">
         <v>9.0</v>
-      </c>
-      <c r="H75" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="76">
@@ -2177,10 +2177,10 @@
         <v>46.0</v>
       </c>
       <c r="G77" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H77" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="78">
@@ -2203,10 +2203,10 @@
         <v>80.0</v>
       </c>
       <c r="G78" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="H78" t="n">
         <v>2.0</v>
-      </c>
-      <c r="H78" t="n">
-        <v>5.0</v>
       </c>
     </row>
     <row r="79">
@@ -2229,10 +2229,10 @@
         <v>65.0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H79" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="80">
@@ -2255,10 +2255,10 @@
         <v>65.0</v>
       </c>
       <c r="G80" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H80" t="n">
         <v>138.0</v>
-      </c>
-      <c r="H80" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="81">
@@ -2281,10 +2281,10 @@
         <v>105.0</v>
       </c>
       <c r="G81" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H81" t="n">
         <v>135.0</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="82">
@@ -2333,10 +2333,10 @@
         <v>0.0</v>
       </c>
       <c r="G83" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H83" t="n">
         <v>15.0</v>
-      </c>
-      <c r="H83" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="84">
@@ -2359,10 +2359,10 @@
         <v>0.0</v>
       </c>
       <c r="G84" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H84" t="n">
         <v>27.0</v>
-      </c>
-      <c r="H84" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="85">
@@ -2411,10 +2411,10 @@
         <v>86.0</v>
       </c>
       <c r="G86" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H86" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="87">
@@ -2457,7 +2457,7 @@
         <v>30</v>
       </c>
       <c r="E88" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F88" t="n">
         <v>1.0</v>
@@ -2483,10 +2483,10 @@
         <v>30</v>
       </c>
       <c r="E89" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F89" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G89" t="n">
         <v>0.0</v>
@@ -2500,19 +2500,19 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C90" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D90" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="E90" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F90" t="n">
-        <v>8.0</v>
+        <v>16.0</v>
       </c>
       <c r="G90" t="n">
         <v>0.0</v>
@@ -2535,10 +2535,10 @@
         <v>17</v>
       </c>
       <c r="E91" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F91" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="G91" t="n">
         <v>0.0</v>
@@ -2561,10 +2561,10 @@
         <v>17</v>
       </c>
       <c r="E92" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F92" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G92" t="n">
         <v>0.0</v>
@@ -2584,16 +2584,16 @@
         <v>12</v>
       </c>
       <c r="D93" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E93" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F93" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G93" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="H93" t="n">
         <v>0.0</v>
@@ -2613,16 +2613,16 @@
         <v>18</v>
       </c>
       <c r="E94" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F94" t="n">
         <v>2.0</v>
       </c>
       <c r="G94" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="95">
@@ -2639,16 +2639,16 @@
         <v>18</v>
       </c>
       <c r="E95" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F95" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H95" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="96">
@@ -2662,10 +2662,10 @@
         <v>12</v>
       </c>
       <c r="D96" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E96" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F96" t="n">
         <v>1.0</v>
@@ -2691,7 +2691,7 @@
         <v>19</v>
       </c>
       <c r="E97" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F97" t="n">
         <v>1.0</v>
@@ -2711,13 +2711,13 @@
         <v>11</v>
       </c>
       <c r="C98" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D98" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E98" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F98" t="n">
         <v>1.0</v>
@@ -2743,10 +2743,10 @@
         <v>28</v>
       </c>
       <c r="E99" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F99" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G99" t="n">
         <v>0.0</v>
@@ -2769,10 +2769,10 @@
         <v>28</v>
       </c>
       <c r="E100" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F100" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G100" t="n">
         <v>0.0</v>
@@ -2792,16 +2792,16 @@
         <v>16</v>
       </c>
       <c r="D101" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E101" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="G101" t="n">
-        <v>5.0</v>
+        <v>0.0</v>
       </c>
       <c r="H101" t="n">
         <v>0.0</v>
@@ -2821,16 +2821,16 @@
         <v>35</v>
       </c>
       <c r="E102" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F102" t="n">
         <v>0.0</v>
       </c>
       <c r="G102" t="n">
-        <v>19.0</v>
+        <v>0.0</v>
       </c>
       <c r="H102" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="103">
@@ -2844,19 +2844,19 @@
         <v>16</v>
       </c>
       <c r="D103" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E103" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F103" t="n">
-        <v>16.0</v>
+        <v>0.0</v>
       </c>
       <c r="G103" t="n">
         <v>0.0</v>
       </c>
       <c r="H103" t="n">
-        <v>0.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="104">
@@ -2873,16 +2873,16 @@
         <v>36</v>
       </c>
       <c r="E104" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F104" t="n">
-        <v>60.0</v>
+        <v>16.0</v>
       </c>
       <c r="G104" t="n">
         <v>0.0</v>
       </c>
       <c r="H104" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="105">
@@ -2899,13 +2899,13 @@
         <v>36</v>
       </c>
       <c r="E105" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F105" t="n">
-        <v>15.0</v>
+        <v>60.0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H105" t="n">
         <v>0.0</v>
@@ -2922,16 +2922,16 @@
         <v>16</v>
       </c>
       <c r="D106" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E106" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F106" t="n">
-        <v>7.0</v>
+        <v>15.0</v>
       </c>
       <c r="G106" t="n">
-        <v>8.0</v>
+        <v>0.0</v>
       </c>
       <c r="H106" t="n">
         <v>0.0</v>
@@ -2951,16 +2951,16 @@
         <v>30</v>
       </c>
       <c r="E107" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F107" t="n">
-        <v>32.0</v>
+        <v>7.0</v>
       </c>
       <c r="G107" t="n">
-        <v>9.0</v>
+        <v>0.0</v>
       </c>
       <c r="H107" t="n">
-        <v>0.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="108">
@@ -2977,15 +2977,41 @@
         <v>30</v>
       </c>
       <c r="E108" t="s">
+        <v>38</v>
+      </c>
+      <c r="F108" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>8</v>
+      </c>
+      <c r="B109" t="s">
+        <v>11</v>
+      </c>
+      <c r="C109" t="s">
+        <v>16</v>
+      </c>
+      <c r="D109" t="s">
+        <v>30</v>
+      </c>
+      <c r="E109" t="s">
         <v>39</v>
       </c>
-      <c r="F108" t="n">
+      <c r="F109" t="n">
         <v>37.0</v>
       </c>
-      <c r="G108" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H108" t="n">
+      <c r="G109" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H109" t="n">
         <v>0.0</v>
       </c>
     </row>
@@ -3016,10 +3042,10 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
         <v>7</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2">
@@ -3059,10 +3085,10 @@
         <v>20</v>
       </c>
       <c r="E3" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="F3" t="n">
         <v>2.0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.0</v>
       </c>
       <c r="G3" t="n">
         <v>0.0</v>
@@ -3099,19 +3125,19 @@
         <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G5" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="6">
@@ -3125,13 +3151,13 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6" t="n">
         <v>14.0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="G6" t="n">
         <v>0.0</v>
@@ -3148,13 +3174,13 @@
         <v>15</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7" t="n">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G7" t="n">
         <v>0.0</v>
@@ -3165,22 +3191,22 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E8" t="n">
-        <v>5.0</v>
+        <v>30.0</v>
       </c>
       <c r="F8" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="G8" t="n">
         <v>1.0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.0</v>
       </c>
     </row>
     <row r="9">
@@ -3194,16 +3220,16 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>30.0</v>
+        <v>190.0</v>
       </c>
       <c r="F9" t="n">
-        <v>15.0</v>
+        <v>113.0</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0</v>
+        <v>274.0</v>
       </c>
     </row>
     <row r="10">
@@ -3217,16 +3243,16 @@
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E10" t="n">
-        <v>190.0</v>
+        <v>47.0</v>
       </c>
       <c r="F10" t="n">
-        <v>113.0</v>
+        <v>49.0</v>
       </c>
       <c r="G10" t="n">
-        <v>274.0</v>
+        <v>20.0</v>
       </c>
     </row>
     <row r="11">
@@ -3240,16 +3266,16 @@
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>47.0</v>
+        <v>0.0</v>
       </c>
       <c r="F11" t="n">
-        <v>50.0</v>
+        <v>0.0</v>
       </c>
       <c r="G11" t="n">
-        <v>20.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="12">
@@ -3263,16 +3289,16 @@
         <v>12</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0</v>
+        <v>30.0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0</v>
+        <v>20.0</v>
       </c>
       <c r="G12" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="13">
@@ -3283,19 +3309,19 @@
         <v>10</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E13" t="n">
-        <v>30.0</v>
+        <v>14.0</v>
       </c>
       <c r="F13" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0</v>
+        <v>50.0</v>
       </c>
     </row>
     <row r="14">
@@ -3309,16 +3335,16 @@
         <v>13</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E14" t="n">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="F14" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G14" t="n">
-        <v>50.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="15">
@@ -3332,16 +3358,16 @@
         <v>13</v>
       </c>
       <c r="D15" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>17.0</v>
+        <v>160.0</v>
       </c>
       <c r="F15" t="n">
-        <v>6.0</v>
+        <v>26.0</v>
       </c>
       <c r="G15" t="n">
-        <v>5.0</v>
+        <v>100.0</v>
       </c>
     </row>
     <row r="16">
@@ -3352,19 +3378,19 @@
         <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E16" t="n">
-        <v>160.0</v>
+        <v>19.0</v>
       </c>
       <c r="F16" t="n">
-        <v>26.0</v>
+        <v>7.0</v>
       </c>
       <c r="G16" t="n">
-        <v>100.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="17">
@@ -3375,19 +3401,19 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E17" t="n">
-        <v>19.0</v>
+        <v>59.0</v>
       </c>
       <c r="F17" t="n">
-        <v>7.0</v>
+        <v>15.0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0</v>
+        <v>37.0</v>
       </c>
     </row>
     <row r="18">
@@ -3401,16 +3427,16 @@
         <v>15</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E18" t="n">
-        <v>58.0</v>
+        <v>4.0</v>
       </c>
       <c r="F18" t="n">
-        <v>15.0</v>
+        <v>5.0</v>
       </c>
       <c r="G18" t="n">
-        <v>37.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="19">
@@ -3424,16 +3450,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>4.0</v>
+        <v>140.0</v>
       </c>
       <c r="F19" t="n">
-        <v>5.0</v>
+        <v>38.0</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0</v>
+        <v>15.0</v>
       </c>
     </row>
     <row r="20">
@@ -3444,19 +3470,19 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E20" t="n">
+        <v>201.0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G20" t="n">
         <v>140.0</v>
-      </c>
-      <c r="F20" t="n">
-        <v>38.0</v>
-      </c>
-      <c r="G20" t="n">
-        <v>15.0</v>
       </c>
     </row>
     <row r="21">
@@ -3470,16 +3496,16 @@
         <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="E21" t="n">
-        <v>201.0</v>
+        <v>0.0</v>
       </c>
       <c r="F21" t="n">
         <v>0.0</v>
       </c>
       <c r="G21" t="n">
-        <v>140.0</v>
+        <v>124.0</v>
       </c>
     </row>
     <row r="22">
@@ -3493,16 +3519,16 @@
         <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0</v>
+        <v>131.0</v>
       </c>
       <c r="F22" t="n">
         <v>0.0</v>
       </c>
       <c r="G22" t="n">
-        <v>124.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="23">
@@ -3510,22 +3536,22 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="E23" t="n">
-        <v>131.0</v>
+        <v>12.0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="24">
@@ -3539,16 +3565,16 @@
         <v>12</v>
       </c>
       <c r="D24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E24" t="n">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G24" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="25">
@@ -3559,19 +3585,19 @@
         <v>11</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D25" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="E25" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>6.0</v>
+        <v>106.0</v>
       </c>
     </row>
     <row r="26">
@@ -3585,16 +3611,16 @@
         <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0</v>
+        <v>80.0</v>
       </c>
       <c r="F26" t="n">
         <v>0.0</v>
       </c>
       <c r="G26" t="n">
-        <v>106.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="27">
@@ -3608,38 +3634,15 @@
         <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E27" t="n">
-        <v>80.0</v>
+        <v>29.0</v>
       </c>
       <c r="F27" t="n">
         <v>0.0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" t="s">
-        <v>16</v>
-      </c>
-      <c r="D28" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28" t="n">
-        <v>29.0</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G28" t="n">
         <v>6.0</v>
       </c>
     </row>
@@ -3670,10 +3673,10 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
         <v>7</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="2">
@@ -3759,7 +3762,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>278.0</v>
+        <v>283.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3782,7 +3785,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>707.0</v>
+        <v>629.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3805,7 +3808,7 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>1338.0</v>
+        <v>1362.0</v>
       </c>
       <c r="F7" t="n">
         <v>0.0</v>
@@ -3828,13 +3831,13 @@
         <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>677.0</v>
+        <v>383.0</v>
       </c>
       <c r="F8" t="n">
         <v>0.0</v>
       </c>
       <c r="G8" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="9">
@@ -3851,13 +3854,13 @@
         <v>24</v>
       </c>
       <c r="E9" t="n">
-        <v>1378.0</v>
+        <v>1371.0</v>
       </c>
       <c r="F9" t="n">
         <v>0.0</v>
       </c>
       <c r="G9" t="n">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
     </row>
     <row r="10">
@@ -3874,7 +3877,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1841.0</v>
+        <v>1845.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -3897,7 +3900,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>619.0</v>
+        <v>628.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3989,7 +3992,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>470.0</v>
+        <v>212.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4081,7 +4084,7 @@
         <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>1567.0</v>
+        <v>1531.0</v>
       </c>
       <c r="F19" t="n">
         <v>0.0</v>
@@ -4150,7 +4153,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9394.0</v>
+        <v>9424.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4173,7 +4176,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3335.0</v>
+        <v>3342.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4196,7 +4199,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6458.0</v>
+        <v>6491.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4219,13 +4222,13 @@
         <v>23</v>
       </c>
       <c r="E25" t="n">
-        <v>3405.0</v>
+        <v>3126.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
       </c>
       <c r="G25" t="n">
-        <v>83.0</v>
+        <v>80.0</v>
       </c>
     </row>
     <row r="26">
@@ -4242,13 +4245,13 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8183.0</v>
+        <v>8145.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
       </c>
       <c r="G26" t="n">
-        <v>214.0</v>
+        <v>213.0</v>
       </c>
     </row>
     <row r="27">
@@ -4265,7 +4268,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>3406.0</v>
+        <v>3415.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4288,7 +4291,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5192.0</v>
+        <v>5219.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>
@@ -4380,7 +4383,7 @@
         <v>30</v>
       </c>
       <c r="E32" t="n">
-        <v>4.0</v>
+        <v>262.0</v>
       </c>
       <c r="F32" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -432,7 +432,7 @@
         <v>39</v>
       </c>
       <c r="F10" t="n">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="G10" t="n">
         <v>0.0</v>
@@ -458,7 +458,7 @@
         <v>37</v>
       </c>
       <c r="F11" t="n">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="G11" t="n">
         <v>0.0</v>
@@ -1706,7 +1706,7 @@
         <v>37</v>
       </c>
       <c r="F59" t="n">
-        <v>1398.0</v>
+        <v>1399.0</v>
       </c>
       <c r="G59" t="n">
         <v>92.0</v>
@@ -1732,7 +1732,7 @@
         <v>38</v>
       </c>
       <c r="F60" t="n">
-        <v>261.0</v>
+        <v>263.0</v>
       </c>
       <c r="G60" t="n">
         <v>25.0</v>
@@ -3206,7 +3206,7 @@
         <v>15.0</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="9">
@@ -3223,10 +3223,10 @@
         <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>190.0</v>
+        <v>192.0</v>
       </c>
       <c r="F9" t="n">
-        <v>113.0</v>
+        <v>114.0</v>
       </c>
       <c r="G9" t="n">
         <v>274.0</v>
@@ -3361,13 +3361,13 @@
         <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>160.0</v>
+        <v>166.0</v>
       </c>
       <c r="F15" t="n">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
       <c r="G15" t="n">
-        <v>100.0</v>
+        <v>101.0</v>
       </c>
     </row>
     <row r="16">
@@ -3453,10 +3453,10 @@
         <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>140.0</v>
+        <v>142.0</v>
       </c>
       <c r="F19" t="n">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="G19" t="n">
         <v>15.0</v>
@@ -3548,7 +3548,7 @@
         <v>12.0</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G23" t="n">
         <v>2.0</v>
@@ -3693,7 +3693,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>145.0</v>
+        <v>167.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -3716,7 +3716,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>384.0</v>
+        <v>406.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3762,7 +3762,7 @@
         <v>20</v>
       </c>
       <c r="E5" t="n">
-        <v>283.0</v>
+        <v>286.0</v>
       </c>
       <c r="F5" t="n">
         <v>0.0</v>
@@ -3785,7 +3785,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>629.0</v>
+        <v>631.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -4038,7 +4038,7 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>457.0</v>
+        <v>462.0</v>
       </c>
       <c r="F17" t="n">
         <v>0.0</v>
@@ -4061,7 +4061,7 @@
         <v>19</v>
       </c>
       <c r="E18" t="n">
-        <v>3566.0</v>
+        <v>3582.0</v>
       </c>
       <c r="F18" t="n">
         <v>2.0</v>
@@ -4084,7 +4084,7 @@
         <v>20</v>
       </c>
       <c r="E19" t="n">
-        <v>1531.0</v>
+        <v>1569.0</v>
       </c>
       <c r="F19" t="n">
         <v>0.0</v>
@@ -4130,7 +4130,7 @@
         <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>659.0</v>
+        <v>675.0</v>
       </c>
       <c r="F21" t="n">
         <v>2.0</v>
@@ -4153,7 +4153,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9424.0</v>
+        <v>9426.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4176,7 +4176,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3342.0</v>
+        <v>3347.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4199,7 +4199,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6491.0</v>
+        <v>6502.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4222,7 +4222,7 @@
         <v>23</v>
       </c>
       <c r="E25" t="n">
-        <v>3126.0</v>
+        <v>3142.0</v>
       </c>
       <c r="F25" t="n">
         <v>0.0</v>
@@ -4245,7 +4245,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8145.0</v>
+        <v>8172.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4268,7 +4268,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>3415.0</v>
+        <v>3417.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4291,7 +4291,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5219.0</v>
+        <v>5223.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -2070,7 +2070,7 @@
         <v>39</v>
       </c>
       <c r="F73" t="n">
-        <v>297.0</v>
+        <v>298.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -3364,7 +3364,7 @@
         <v>166.0</v>
       </c>
       <c r="F15" t="n">
-        <v>28.0</v>
+        <v>31.0</v>
       </c>
       <c r="G15" t="n">
         <v>101.0</v>
@@ -3453,7 +3453,7 @@
         <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>142.0</v>
+        <v>143.0</v>
       </c>
       <c r="F19" t="n">
         <v>39.0</v>
@@ -3808,7 +3808,7 @@
         <v>22</v>
       </c>
       <c r="E7" t="n">
-        <v>1362.0</v>
+        <v>1403.0</v>
       </c>
       <c r="F7" t="n">
         <v>0.0</v>
@@ -3877,7 +3877,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1845.0</v>
+        <v>1858.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -3900,7 +3900,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="n">
-        <v>628.0</v>
+        <v>647.0</v>
       </c>
       <c r="F11" t="n">
         <v>0.0</v>
@@ -3992,7 +3992,7 @@
         <v>30</v>
       </c>
       <c r="E15" t="n">
-        <v>212.0</v>
+        <v>213.0</v>
       </c>
       <c r="F15" t="n">
         <v>0.0</v>
@@ -4015,7 +4015,7 @@
         <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>92.0</v>
+        <v>106.0</v>
       </c>
       <c r="F16" t="n">
         <v>0.0</v>
@@ -4153,7 +4153,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9426.0</v>
+        <v>9495.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4176,7 +4176,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3347.0</v>
+        <v>3405.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4199,7 +4199,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6502.0</v>
+        <v>6580.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4245,7 +4245,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8172.0</v>
+        <v>8180.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4268,7 +4268,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>3417.0</v>
+        <v>3440.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4291,7 +4291,7 @@
         <v>26</v>
       </c>
       <c r="E28" t="n">
-        <v>5223.0</v>
+        <v>5281.0</v>
       </c>
       <c r="F28" t="n">
         <v>1.0</v>
@@ -4360,7 +4360,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>2011.0</v>
+        <v>2066.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4383,7 +4383,7 @@
         <v>30</v>
       </c>
       <c r="E32" t="n">
-        <v>262.0</v>
+        <v>268.0</v>
       </c>
       <c r="F32" t="n">
         <v>0.0</v>
@@ -4544,7 +4544,7 @@
         <v>36</v>
       </c>
       <c r="E39" t="n">
-        <v>1380.0</v>
+        <v>1404.0</v>
       </c>
       <c r="F39" t="n">
         <v>0.0</v>
@@ -4567,7 +4567,7 @@
         <v>30</v>
       </c>
       <c r="E40" t="n">
-        <v>1176.0</v>
+        <v>1181.0</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -588,7 +588,7 @@
         <v>39</v>
       </c>
       <c r="F16" t="n">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="G16" t="n">
         <v>0.0</v>
@@ -1550,7 +1550,7 @@
         <v>39</v>
       </c>
       <c r="F53" t="n">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1706,7 +1706,7 @@
         <v>37</v>
       </c>
       <c r="F59" t="n">
-        <v>1399.0</v>
+        <v>1400.0</v>
       </c>
       <c r="G59" t="n">
         <v>92.0</v>
@@ -2070,7 +2070,7 @@
         <v>39</v>
       </c>
       <c r="F73" t="n">
-        <v>298.0</v>
+        <v>301.0</v>
       </c>
       <c r="G73" t="n">
         <v>0.0</v>
@@ -2252,7 +2252,7 @@
         <v>37</v>
       </c>
       <c r="F80" t="n">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="G80" t="n">
         <v>1.0</v>
@@ -3223,7 +3223,7 @@
         <v>19</v>
       </c>
       <c r="E9" t="n">
-        <v>192.0</v>
+        <v>196.0</v>
       </c>
       <c r="F9" t="n">
         <v>114.0</v>
@@ -3453,10 +3453,10 @@
         <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>143.0</v>
+        <v>149.0</v>
       </c>
       <c r="F19" t="n">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="G19" t="n">
         <v>15.0</v>
@@ -3693,7 +3693,7 @@
         <v>17</v>
       </c>
       <c r="E2" t="n">
-        <v>167.0</v>
+        <v>169.0</v>
       </c>
       <c r="F2" t="n">
         <v>0.0</v>
@@ -3716,7 +3716,7 @@
         <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>406.0</v>
+        <v>410.0</v>
       </c>
       <c r="F3" t="n">
         <v>0.0</v>
@@ -3785,7 +3785,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>631.0</v>
+        <v>638.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3877,7 +3877,7 @@
         <v>25</v>
       </c>
       <c r="E10" t="n">
-        <v>1858.0</v>
+        <v>1873.0</v>
       </c>
       <c r="F10" t="n">
         <v>1.0</v>
@@ -4153,7 +4153,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9495.0</v>
+        <v>9497.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4176,7 +4176,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3405.0</v>
+        <v>3413.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4199,7 +4199,7 @@
         <v>22</v>
       </c>
       <c r="E24" t="n">
-        <v>6580.0</v>
+        <v>6581.0</v>
       </c>
       <c r="F24" t="n">
         <v>0.0</v>
@@ -4245,7 +4245,7 @@
         <v>24</v>
       </c>
       <c r="E26" t="n">
-        <v>8180.0</v>
+        <v>8204.0</v>
       </c>
       <c r="F26" t="n">
         <v>3.0</v>
@@ -4268,7 +4268,7 @@
         <v>25</v>
       </c>
       <c r="E27" t="n">
-        <v>3440.0</v>
+        <v>3450.0</v>
       </c>
       <c r="F27" t="n">
         <v>1.0</v>
@@ -4297,7 +4297,7 @@
         <v>1.0</v>
       </c>
       <c r="G28" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="29">
@@ -4314,7 +4314,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1310.0</v>
+        <v>1335.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>

--- a/Download/wild_boar_ZR.xlsx
+++ b/Download/wild_boar_ZR.xlsx
@@ -1550,7 +1550,7 @@
         <v>39</v>
       </c>
       <c r="F53" t="n">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="G53" t="n">
         <v>0.0</v>
@@ -1862,7 +1862,7 @@
         <v>37</v>
       </c>
       <c r="F65" t="n">
-        <v>252.0</v>
+        <v>253.0</v>
       </c>
       <c r="G65" t="n">
         <v>6.0</v>
@@ -1914,7 +1914,7 @@
         <v>39</v>
       </c>
       <c r="F67" t="n">
-        <v>122.0</v>
+        <v>123.0</v>
       </c>
       <c r="G67" t="n">
         <v>1.0</v>
@@ -3229,7 +3229,7 @@
         <v>114.0</v>
       </c>
       <c r="G9" t="n">
-        <v>274.0</v>
+        <v>275.0</v>
       </c>
     </row>
     <row r="10">
@@ -3361,10 +3361,10 @@
         <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>166.0</v>
+        <v>168.0</v>
       </c>
       <c r="F15" t="n">
-        <v>31.0</v>
+        <v>34.0</v>
       </c>
       <c r="G15" t="n">
         <v>101.0</v>
@@ -3453,7 +3453,7 @@
         <v>26</v>
       </c>
       <c r="E19" t="n">
-        <v>149.0</v>
+        <v>150.0</v>
       </c>
       <c r="F19" t="n">
         <v>40.0</v>
@@ -3785,7 +3785,7 @@
         <v>21</v>
       </c>
       <c r="E6" t="n">
-        <v>638.0</v>
+        <v>640.0</v>
       </c>
       <c r="F6" t="n">
         <v>0.0</v>
@@ -3946,7 +3946,7 @@
         <v>28</v>
       </c>
       <c r="E13" t="n">
-        <v>112.0</v>
+        <v>114.0</v>
       </c>
       <c r="F13" t="n">
         <v>0.0</v>
@@ -4015,7 +4015,7 @@
         <v>31</v>
       </c>
       <c r="E16" t="n">
-        <v>106.0</v>
+        <v>114.0</v>
       </c>
       <c r="F16" t="n">
         <v>0.0</v>
@@ -4153,7 +4153,7 @@
         <v>33</v>
       </c>
       <c r="E22" t="n">
-        <v>9497.0</v>
+        <v>9508.0</v>
       </c>
       <c r="F22" t="n">
         <v>18.0</v>
@@ -4176,7 +4176,7 @@
         <v>34</v>
       </c>
       <c r="E23" t="n">
-        <v>3413.0</v>
+        <v>3422.0</v>
       </c>
       <c r="F23" t="n">
         <v>0.0</v>
@@ -4314,7 +4314,7 @@
         <v>28</v>
       </c>
       <c r="E29" t="n">
-        <v>1335.0</v>
+        <v>1338.0</v>
       </c>
       <c r="F29" t="n">
         <v>0.0</v>
@@ -4360,7 +4360,7 @@
         <v>36</v>
       </c>
       <c r="E31" t="n">
-        <v>2066.0</v>
+        <v>2091.0</v>
       </c>
       <c r="F31" t="n">
         <v>0.0</v>
@@ -4544,7 +4544,7 @@
         <v>36</v>
       </c>
       <c r="E39" t="n">
-        <v>1404.0</v>
+        <v>1414.0</v>
       </c>
       <c r="F39" t="n">
         <v>0.0</v>
